--- a/automation/reports/Excel/Passed_Test_Cases.xlsx
+++ b/automation/reports/Excel/Passed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="1031">
   <si>
     <t>Test ID</t>
   </si>
@@ -133,6 +133,12 @@
     <t>Verify Authentication Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-AUTH-015</t>
+  </si>
+  <si>
+    <t>Verify Authentication Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-AUTH-016</t>
   </si>
   <si>
@@ -217,6 +223,12 @@
     <t>Verify Authentication Functionality &amp; Boundary Scenario #29</t>
   </si>
   <si>
+    <t>TC-AUTH-030</t>
+  </si>
+  <si>
+    <t>Verify Authentication Functionality &amp; Boundary Scenario #30</t>
+  </si>
+  <si>
     <t>TC-AUTH-031</t>
   </si>
   <si>
@@ -241,6 +253,12 @@
     <t>Verify Authentication Functionality &amp; Boundary Scenario #34</t>
   </si>
   <si>
+    <t>TC-AUTH-035</t>
+  </si>
+  <si>
+    <t>Verify Authentication Functionality &amp; Boundary Scenario #35</t>
+  </si>
+  <si>
     <t>TC-AUTH-036</t>
   </si>
   <si>
@@ -358,6 +376,12 @@
     <t>Verify Authorization Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-AUTHZ-015</t>
+  </si>
+  <si>
+    <t>Verify Authorization Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-AUTHZ-016</t>
   </si>
   <si>
@@ -442,6 +466,12 @@
     <t>Verify Authorization Functionality &amp; Boundary Scenario #29</t>
   </si>
   <si>
+    <t>TC-AUTHZ-030</t>
+  </si>
+  <si>
+    <t>Verify Authorization Functionality &amp; Boundary Scenario #30</t>
+  </si>
+  <si>
     <t>TC-REG-001</t>
   </si>
   <si>
@@ -529,6 +559,12 @@
     <t>Verify Registration Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-REG-015</t>
+  </si>
+  <si>
+    <t>Verify Registration Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-REG-016</t>
   </si>
   <si>
@@ -646,6 +682,12 @@
     <t>Verify Profile Management Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-PROF-015</t>
+  </si>
+  <si>
+    <t>Verify Profile Management Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-PROF-016</t>
   </si>
   <si>
@@ -763,6 +805,12 @@
     <t>Verify Navigation Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-NAV-015</t>
+  </si>
+  <si>
+    <t>Verify Navigation Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-NAV-016</t>
   </si>
   <si>
@@ -847,6 +895,12 @@
     <t>Verify Navigation Functionality &amp; Boundary Scenario #29</t>
   </si>
   <si>
+    <t>TC-NAV-030</t>
+  </si>
+  <si>
+    <t>Verify Navigation Functionality &amp; Boundary Scenario #30</t>
+  </si>
+  <si>
     <t>TC-DASH-001</t>
   </si>
   <si>
@@ -934,6 +988,12 @@
     <t>Verify Dashboard Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-DASH-015</t>
+  </si>
+  <si>
+    <t>Verify Dashboard Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-DASH-016</t>
   </si>
   <si>
@@ -1051,6 +1111,12 @@
     <t>Verify Forms Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-FORM-015</t>
+  </si>
+  <si>
+    <t>Verify Forms Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-FORM-016</t>
   </si>
   <si>
@@ -1135,6 +1201,12 @@
     <t>Verify Forms Functionality &amp; Boundary Scenario #29</t>
   </si>
   <si>
+    <t>TC-FORM-030</t>
+  </si>
+  <si>
+    <t>Verify Forms Functionality &amp; Boundary Scenario #30</t>
+  </si>
+  <si>
     <t>TC-FORM-031</t>
   </si>
   <si>
@@ -1159,6 +1231,12 @@
     <t>Verify Forms Functionality &amp; Boundary Scenario #34</t>
   </si>
   <si>
+    <t>TC-FORM-035</t>
+  </si>
+  <si>
+    <t>Verify Forms Functionality &amp; Boundary Scenario #35</t>
+  </si>
+  <si>
     <t>TC-FORM-036</t>
   </si>
   <si>
@@ -1276,6 +1354,12 @@
     <t>Verify CRUD Operations Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-CRUD-015</t>
+  </si>
+  <si>
+    <t>Verify CRUD Operations Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-CRUD-016</t>
   </si>
   <si>
@@ -1360,6 +1444,12 @@
     <t>Verify CRUD Operations Functionality &amp; Boundary Scenario #29</t>
   </si>
   <si>
+    <t>TC-CRUD-030</t>
+  </si>
+  <si>
+    <t>Verify CRUD Operations Functionality &amp; Boundary Scenario #30</t>
+  </si>
+  <si>
     <t>TC-CRUD-031</t>
   </si>
   <si>
@@ -1384,6 +1474,12 @@
     <t>Verify CRUD Operations Functionality &amp; Boundary Scenario #34</t>
   </si>
   <si>
+    <t>TC-CRUD-035</t>
+  </si>
+  <si>
+    <t>Verify CRUD Operations Functionality &amp; Boundary Scenario #35</t>
+  </si>
+  <si>
     <t>TC-CRUD-036</t>
   </si>
   <si>
@@ -1501,6 +1597,12 @@
     <t>Verify Search Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-SRCH-015</t>
+  </si>
+  <si>
+    <t>Verify Search Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-SRCH-016</t>
   </si>
   <si>
@@ -1618,6 +1720,12 @@
     <t>Verify Filters Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-FLTR-015</t>
+  </si>
+  <si>
+    <t>Verify Filters Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-FLTR-016</t>
   </si>
   <si>
@@ -1735,6 +1843,12 @@
     <t>Verify Input Validation Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-VAL-015</t>
+  </si>
+  <si>
+    <t>Verify Input Validation Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-VAL-016</t>
   </si>
   <si>
@@ -1819,6 +1933,12 @@
     <t>Verify Input Validation Functionality &amp; Boundary Scenario #29</t>
   </si>
   <si>
+    <t>TC-VAL-030</t>
+  </si>
+  <si>
+    <t>Verify Input Validation Functionality &amp; Boundary Scenario #30</t>
+  </si>
+  <si>
     <t>TC-VAL-031</t>
   </si>
   <si>
@@ -1843,6 +1963,12 @@
     <t>Verify Input Validation Functionality &amp; Boundary Scenario #34</t>
   </si>
   <si>
+    <t>TC-VAL-035</t>
+  </si>
+  <si>
+    <t>Verify Input Validation Functionality &amp; Boundary Scenario #35</t>
+  </si>
+  <si>
     <t>TC-VAL-036</t>
   </si>
   <si>
@@ -1960,6 +2086,12 @@
     <t>Verify Error Handling Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-ERR-015</t>
+  </si>
+  <si>
+    <t>Verify Error Handling Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-ERR-016</t>
   </si>
   <si>
@@ -2077,6 +2209,12 @@
     <t>Verify Session Management Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-SESS-015</t>
+  </si>
+  <si>
+    <t>Verify Session Management Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-SESS-016</t>
   </si>
   <si>
@@ -2194,6 +2332,12 @@
     <t>Verify Notifications Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-NOTIF-015</t>
+  </si>
+  <si>
+    <t>Verify Notifications Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-NOTIF-016</t>
   </si>
   <si>
@@ -2311,6 +2455,12 @@
     <t>Verify File Upload Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-UPLD-015</t>
+  </si>
+  <si>
+    <t>Verify File Upload Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-UPLD-016</t>
   </si>
   <si>
@@ -2491,6 +2641,12 @@
     <t>Verify Accessibility Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-A11Y-015</t>
+  </si>
+  <si>
+    <t>Verify Accessibility Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-A11Y-016</t>
   </si>
   <si>
@@ -2671,6 +2827,12 @@
     <t>Verify Performance Smoke Tests Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>TC-PERF-015</t>
+  </si>
+  <si>
+    <t>Verify Performance Smoke Tests Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>TC-PERF-016</t>
   </si>
   <si>
@@ -2746,6 +2908,9 @@
     <t>Verify Regression Suite Functionality &amp; Boundary Scenario #14</t>
   </si>
   <si>
+    <t>Verify Regression Suite Functionality &amp; Boundary Scenario #15</t>
+  </si>
+  <si>
     <t>Verify Regression Suite Functionality &amp; Boundary Scenario #16</t>
   </si>
   <si>
@@ -2815,6 +2980,12 @@
     <t>Verify Regression Suite Functionality &amp; Boundary Scenario #29</t>
   </si>
   <si>
+    <t>TC-REG-030</t>
+  </si>
+  <si>
+    <t>Verify Regression Suite Functionality &amp; Boundary Scenario #30</t>
+  </si>
+  <si>
     <t>TC-REG-031</t>
   </si>
   <si>
@@ -2839,6 +3010,12 @@
     <t>Verify Regression Suite Functionality &amp; Boundary Scenario #34</t>
   </si>
   <si>
+    <t>TC-REG-035</t>
+  </si>
+  <si>
+    <t>Verify Regression Suite Functionality &amp; Boundary Scenario #35</t>
+  </si>
+  <si>
     <t>TC-REG-036</t>
   </si>
   <si>
@@ -2891,6 +3068,12 @@
   </si>
   <si>
     <t>Verify Regression Suite Functionality &amp; Boundary Scenario #44</t>
+  </si>
+  <si>
+    <t>TC-REG-045</t>
+  </si>
+  <si>
+    <t>Verify Regression Suite Functionality &amp; Boundary Scenario #45</t>
   </si>
   <si>
     <t>TC-REG-046</t>
@@ -3297,7 +3480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F480"/>
+  <dimension ref="A1:F511"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3618,7 +3801,7 @@
         <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -3638,7 +3821,7 @@
         <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -3658,7 +3841,7 @@
         <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -3678,7 +3861,7 @@
         <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -3698,7 +3881,7 @@
         <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -3718,7 +3901,7 @@
         <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -3738,7 +3921,7 @@
         <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -3758,7 +3941,7 @@
         <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -3778,7 +3961,7 @@
         <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -3798,7 +3981,7 @@
         <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -3818,7 +4001,7 @@
         <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -3838,7 +4021,7 @@
         <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -3858,7 +4041,7 @@
         <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -3878,7 +4061,7 @@
         <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -3898,7 +4081,7 @@
         <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -3918,7 +4101,7 @@
         <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -3938,7 +4121,7 @@
         <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -3958,7 +4141,7 @@
         <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -3978,7 +4161,7 @@
         <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -3998,7 +4181,7 @@
         <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -4018,7 +4201,7 @@
         <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -4038,7 +4221,7 @@
         <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -4058,7 +4241,7 @@
         <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -4072,13 +4255,13 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
         <v>87</v>
       </c>
-      <c r="C39" t="s">
-        <v>88</v>
-      </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -4089,16 +4272,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
         <v>89</v>
       </c>
-      <c r="B40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" t="s">
-        <v>90</v>
-      </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -4109,16 +4292,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
         <v>91</v>
       </c>
-      <c r="B41" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" t="s">
-        <v>92</v>
-      </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -4129,16 +4312,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
         <v>93</v>
-      </c>
-      <c r="B42" t="s">
-        <v>87</v>
       </c>
       <c r="C42" t="s">
         <v>94</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -4152,13 +4335,13 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s">
         <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
@@ -4172,13 +4355,13 @@
         <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C44" t="s">
         <v>98</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -4192,13 +4375,13 @@
         <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
         <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -4212,13 +4395,13 @@
         <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C46" t="s">
         <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
@@ -4232,13 +4415,13 @@
         <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
@@ -4252,13 +4435,13 @@
         <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
         <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
@@ -4272,13 +4455,13 @@
         <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
         <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
@@ -4292,13 +4475,13 @@
         <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s">
         <v>110</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
@@ -4312,13 +4495,13 @@
         <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
         <v>112</v>
       </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
@@ -4332,13 +4515,13 @@
         <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C52" t="s">
         <v>114</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -4352,7 +4535,7 @@
         <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C53" t="s">
         <v>116</v>
@@ -4372,7 +4555,7 @@
         <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
         <v>118</v>
@@ -4392,7 +4575,7 @@
         <v>119</v>
       </c>
       <c r="B55" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C55" t="s">
         <v>120</v>
@@ -4412,7 +4595,7 @@
         <v>121</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C56" t="s">
         <v>122</v>
@@ -4432,7 +4615,7 @@
         <v>123</v>
       </c>
       <c r="B57" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C57" t="s">
         <v>124</v>
@@ -4452,7 +4635,7 @@
         <v>125</v>
       </c>
       <c r="B58" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C58" t="s">
         <v>126</v>
@@ -4472,7 +4655,7 @@
         <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
         <v>128</v>
@@ -4492,7 +4675,7 @@
         <v>129</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
         <v>130</v>
@@ -4512,7 +4695,7 @@
         <v>131</v>
       </c>
       <c r="B61" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C61" t="s">
         <v>132</v>
@@ -4532,7 +4715,7 @@
         <v>133</v>
       </c>
       <c r="B62" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C62" t="s">
         <v>134</v>
@@ -4552,7 +4735,7 @@
         <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C63" t="s">
         <v>136</v>
@@ -4572,7 +4755,7 @@
         <v>137</v>
       </c>
       <c r="B64" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C64" t="s">
         <v>138</v>
@@ -4592,7 +4775,7 @@
         <v>139</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C65" t="s">
         <v>140</v>
@@ -4612,7 +4795,7 @@
         <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C66" t="s">
         <v>142</v>
@@ -4632,13 +4815,13 @@
         <v>143</v>
       </c>
       <c r="B67" t="s">
+        <v>93</v>
+      </c>
+      <c r="C67" t="s">
         <v>144</v>
       </c>
-      <c r="C67" t="s">
-        <v>145</v>
-      </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -4649,16 +4832,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68" t="s">
         <v>146</v>
       </c>
-      <c r="B68" t="s">
-        <v>144</v>
-      </c>
-      <c r="C68" t="s">
-        <v>147</v>
-      </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -4669,16 +4852,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>147</v>
+      </c>
+      <c r="B69" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" t="s">
         <v>148</v>
       </c>
-      <c r="B69" t="s">
-        <v>144</v>
-      </c>
-      <c r="C69" t="s">
-        <v>149</v>
-      </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -4689,16 +4872,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>149</v>
+      </c>
+      <c r="B70" t="s">
+        <v>93</v>
+      </c>
+      <c r="C70" t="s">
         <v>150</v>
       </c>
-      <c r="B70" t="s">
-        <v>144</v>
-      </c>
-      <c r="C70" t="s">
-        <v>151</v>
-      </c>
       <c r="D70" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -4709,16 +4892,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>151</v>
+      </c>
+      <c r="B71" t="s">
+        <v>93</v>
+      </c>
+      <c r="C71" t="s">
         <v>152</v>
       </c>
-      <c r="B71" t="s">
-        <v>144</v>
-      </c>
-      <c r="C71" t="s">
-        <v>153</v>
-      </c>
       <c r="D71" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
@@ -4729,16 +4912,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>153</v>
+      </c>
+      <c r="B72" t="s">
         <v>154</v>
-      </c>
-      <c r="B72" t="s">
-        <v>144</v>
       </c>
       <c r="C72" t="s">
         <v>155</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -4752,13 +4935,13 @@
         <v>156</v>
       </c>
       <c r="B73" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C73" t="s">
         <v>157</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
@@ -4772,13 +4955,13 @@
         <v>158</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C74" t="s">
         <v>159</v>
       </c>
       <c r="D74" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
@@ -4792,13 +4975,13 @@
         <v>160</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C75" t="s">
         <v>161</v>
       </c>
       <c r="D75" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
@@ -4812,13 +4995,13 @@
         <v>162</v>
       </c>
       <c r="B76" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C76" t="s">
         <v>163</v>
       </c>
       <c r="D76" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
@@ -4832,13 +5015,13 @@
         <v>164</v>
       </c>
       <c r="B77" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C77" t="s">
         <v>165</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
@@ -4852,13 +5035,13 @@
         <v>166</v>
       </c>
       <c r="B78" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C78" t="s">
         <v>167</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
@@ -4872,13 +5055,13 @@
         <v>168</v>
       </c>
       <c r="B79" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C79" t="s">
         <v>169</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
@@ -4892,13 +5075,13 @@
         <v>170</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C80" t="s">
         <v>171</v>
       </c>
       <c r="D80" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
@@ -4912,13 +5095,13 @@
         <v>172</v>
       </c>
       <c r="B81" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C81" t="s">
         <v>173</v>
       </c>
       <c r="D81" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
@@ -4932,13 +5115,13 @@
         <v>174</v>
       </c>
       <c r="B82" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C82" t="s">
         <v>175</v>
       </c>
       <c r="D82" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
@@ -4952,13 +5135,13 @@
         <v>176</v>
       </c>
       <c r="B83" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C83" t="s">
         <v>177</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
@@ -4972,13 +5155,13 @@
         <v>178</v>
       </c>
       <c r="B84" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C84" t="s">
         <v>179</v>
       </c>
       <c r="D84" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
@@ -4992,13 +5175,13 @@
         <v>180</v>
       </c>
       <c r="B85" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C85" t="s">
         <v>181</v>
       </c>
       <c r="D85" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
@@ -5012,13 +5195,13 @@
         <v>182</v>
       </c>
       <c r="B86" t="s">
+        <v>154</v>
+      </c>
+      <c r="C86" t="s">
         <v>183</v>
       </c>
-      <c r="C86" t="s">
-        <v>184</v>
-      </c>
       <c r="D86" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
@@ -5029,16 +5212,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>184</v>
+      </c>
+      <c r="B87" t="s">
+        <v>154</v>
+      </c>
+      <c r="C87" t="s">
         <v>185</v>
       </c>
-      <c r="B87" t="s">
-        <v>183</v>
-      </c>
-      <c r="C87" t="s">
-        <v>186</v>
-      </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -5049,16 +5232,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" t="s">
         <v>187</v>
       </c>
-      <c r="B88" t="s">
-        <v>183</v>
-      </c>
-      <c r="C88" t="s">
-        <v>188</v>
-      </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -5069,16 +5252,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" t="s">
+        <v>154</v>
+      </c>
+      <c r="C89" t="s">
         <v>189</v>
       </c>
-      <c r="B89" t="s">
-        <v>183</v>
-      </c>
-      <c r="C89" t="s">
-        <v>190</v>
-      </c>
       <c r="D89" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -5089,16 +5272,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>190</v>
+      </c>
+      <c r="B90" t="s">
+        <v>154</v>
+      </c>
+      <c r="C90" t="s">
         <v>191</v>
       </c>
-      <c r="B90" t="s">
-        <v>183</v>
-      </c>
-      <c r="C90" t="s">
-        <v>192</v>
-      </c>
       <c r="D90" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -5109,16 +5292,16 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>192</v>
+      </c>
+      <c r="B91" t="s">
+        <v>154</v>
+      </c>
+      <c r="C91" t="s">
         <v>193</v>
       </c>
-      <c r="B91" t="s">
-        <v>183</v>
-      </c>
-      <c r="C91" t="s">
-        <v>194</v>
-      </c>
       <c r="D91" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -5129,16 +5312,16 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>194</v>
+      </c>
+      <c r="B92" t="s">
         <v>195</v>
-      </c>
-      <c r="B92" t="s">
-        <v>183</v>
       </c>
       <c r="C92" t="s">
         <v>196</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
@@ -5152,13 +5335,13 @@
         <v>197</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C93" t="s">
         <v>198</v>
       </c>
       <c r="D93" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
@@ -5172,13 +5355,13 @@
         <v>199</v>
       </c>
       <c r="B94" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C94" t="s">
         <v>200</v>
       </c>
       <c r="D94" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
@@ -5192,13 +5375,13 @@
         <v>201</v>
       </c>
       <c r="B95" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C95" t="s">
         <v>202</v>
       </c>
       <c r="D95" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
@@ -5212,13 +5395,13 @@
         <v>203</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C96" t="s">
         <v>204</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -5232,13 +5415,13 @@
         <v>205</v>
       </c>
       <c r="B97" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C97" t="s">
         <v>206</v>
       </c>
       <c r="D97" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
@@ -5252,13 +5435,13 @@
         <v>207</v>
       </c>
       <c r="B98" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C98" t="s">
         <v>208</v>
       </c>
       <c r="D98" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
@@ -5272,13 +5455,13 @@
         <v>209</v>
       </c>
       <c r="B99" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C99" t="s">
         <v>210</v>
       </c>
       <c r="D99" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
@@ -5292,13 +5475,13 @@
         <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C100" t="s">
         <v>212</v>
       </c>
       <c r="D100" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -5312,13 +5495,13 @@
         <v>213</v>
       </c>
       <c r="B101" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C101" t="s">
         <v>214</v>
       </c>
       <c r="D101" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
@@ -5332,13 +5515,13 @@
         <v>215</v>
       </c>
       <c r="B102" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C102" t="s">
         <v>216</v>
       </c>
       <c r="D102" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
@@ -5352,13 +5535,13 @@
         <v>217</v>
       </c>
       <c r="B103" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C103" t="s">
         <v>218</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
@@ -5372,13 +5555,13 @@
         <v>219</v>
       </c>
       <c r="B104" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C104" t="s">
         <v>220</v>
       </c>
       <c r="D104" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
@@ -5392,13 +5575,13 @@
         <v>221</v>
       </c>
       <c r="B105" t="s">
+        <v>195</v>
+      </c>
+      <c r="C105" t="s">
         <v>222</v>
       </c>
-      <c r="C105" t="s">
-        <v>223</v>
-      </c>
       <c r="D105" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -5409,16 +5592,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>223</v>
+      </c>
+      <c r="B106" t="s">
+        <v>195</v>
+      </c>
+      <c r="C106" t="s">
         <v>224</v>
       </c>
-      <c r="B106" t="s">
-        <v>222</v>
-      </c>
-      <c r="C106" t="s">
-        <v>225</v>
-      </c>
       <c r="D106" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
@@ -5429,16 +5612,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>225</v>
+      </c>
+      <c r="B107" t="s">
+        <v>195</v>
+      </c>
+      <c r="C107" t="s">
         <v>226</v>
       </c>
-      <c r="B107" t="s">
-        <v>222</v>
-      </c>
-      <c r="C107" t="s">
-        <v>227</v>
-      </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
@@ -5449,16 +5632,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>227</v>
+      </c>
+      <c r="B108" t="s">
+        <v>195</v>
+      </c>
+      <c r="C108" t="s">
         <v>228</v>
       </c>
-      <c r="B108" t="s">
-        <v>222</v>
-      </c>
-      <c r="C108" t="s">
-        <v>229</v>
-      </c>
       <c r="D108" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
@@ -5469,16 +5652,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>229</v>
+      </c>
+      <c r="B109" t="s">
+        <v>195</v>
+      </c>
+      <c r="C109" t="s">
         <v>230</v>
       </c>
-      <c r="B109" t="s">
-        <v>222</v>
-      </c>
-      <c r="C109" t="s">
-        <v>231</v>
-      </c>
       <c r="D109" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
@@ -5489,16 +5672,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>231</v>
+      </c>
+      <c r="B110" t="s">
+        <v>195</v>
+      </c>
+      <c r="C110" t="s">
         <v>232</v>
       </c>
-      <c r="B110" t="s">
-        <v>222</v>
-      </c>
-      <c r="C110" t="s">
-        <v>233</v>
-      </c>
       <c r="D110" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
@@ -5509,16 +5692,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>233</v>
+      </c>
+      <c r="B111" t="s">
+        <v>195</v>
+      </c>
+      <c r="C111" t="s">
         <v>234</v>
       </c>
-      <c r="B111" t="s">
-        <v>222</v>
-      </c>
-      <c r="C111" t="s">
-        <v>235</v>
-      </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
@@ -5529,16 +5712,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>235</v>
+      </c>
+      <c r="B112" t="s">
         <v>236</v>
-      </c>
-      <c r="B112" t="s">
-        <v>222</v>
       </c>
       <c r="C112" t="s">
         <v>237</v>
       </c>
       <c r="D112" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
@@ -5552,13 +5735,13 @@
         <v>238</v>
       </c>
       <c r="B113" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C113" t="s">
         <v>239</v>
       </c>
       <c r="D113" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
@@ -5572,13 +5755,13 @@
         <v>240</v>
       </c>
       <c r="B114" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C114" t="s">
         <v>241</v>
       </c>
       <c r="D114" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
@@ -5592,13 +5775,13 @@
         <v>242</v>
       </c>
       <c r="B115" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C115" t="s">
         <v>243</v>
       </c>
       <c r="D115" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
@@ -5612,13 +5795,13 @@
         <v>244</v>
       </c>
       <c r="B116" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C116" t="s">
         <v>245</v>
       </c>
       <c r="D116" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
@@ -5632,13 +5815,13 @@
         <v>246</v>
       </c>
       <c r="B117" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C117" t="s">
         <v>247</v>
       </c>
       <c r="D117" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
@@ -5652,13 +5835,13 @@
         <v>248</v>
       </c>
       <c r="B118" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C118" t="s">
         <v>249</v>
       </c>
       <c r="D118" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E118" t="s">
         <v>10</v>
@@ -5672,7 +5855,7 @@
         <v>250</v>
       </c>
       <c r="B119" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C119" t="s">
         <v>251</v>
@@ -5692,7 +5875,7 @@
         <v>252</v>
       </c>
       <c r="B120" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C120" t="s">
         <v>253</v>
@@ -5712,7 +5895,7 @@
         <v>254</v>
       </c>
       <c r="B121" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C121" t="s">
         <v>255</v>
@@ -5732,7 +5915,7 @@
         <v>256</v>
       </c>
       <c r="B122" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C122" t="s">
         <v>257</v>
@@ -5752,7 +5935,7 @@
         <v>258</v>
       </c>
       <c r="B123" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C123" t="s">
         <v>259</v>
@@ -5772,7 +5955,7 @@
         <v>260</v>
       </c>
       <c r="B124" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C124" t="s">
         <v>261</v>
@@ -5792,7 +5975,7 @@
         <v>262</v>
       </c>
       <c r="B125" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C125" t="s">
         <v>263</v>
@@ -5812,7 +5995,7 @@
         <v>264</v>
       </c>
       <c r="B126" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C126" t="s">
         <v>265</v>
@@ -5832,7 +6015,7 @@
         <v>266</v>
       </c>
       <c r="B127" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C127" t="s">
         <v>267</v>
@@ -5852,7 +6035,7 @@
         <v>268</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C128" t="s">
         <v>269</v>
@@ -5872,7 +6055,7 @@
         <v>270</v>
       </c>
       <c r="B129" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C129" t="s">
         <v>271</v>
@@ -5892,7 +6075,7 @@
         <v>272</v>
       </c>
       <c r="B130" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C130" t="s">
         <v>273</v>
@@ -5912,7 +6095,7 @@
         <v>274</v>
       </c>
       <c r="B131" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C131" t="s">
         <v>275</v>
@@ -5932,7 +6115,7 @@
         <v>276</v>
       </c>
       <c r="B132" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C132" t="s">
         <v>277</v>
@@ -5952,13 +6135,13 @@
         <v>278</v>
       </c>
       <c r="B133" t="s">
+        <v>236</v>
+      </c>
+      <c r="C133" t="s">
         <v>279</v>
       </c>
-      <c r="C133" t="s">
-        <v>280</v>
-      </c>
       <c r="D133" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -5969,16 +6152,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>280</v>
+      </c>
+      <c r="B134" t="s">
+        <v>236</v>
+      </c>
+      <c r="C134" t="s">
         <v>281</v>
       </c>
-      <c r="B134" t="s">
-        <v>279</v>
-      </c>
-      <c r="C134" t="s">
-        <v>282</v>
-      </c>
       <c r="D134" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
@@ -5989,16 +6172,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>282</v>
+      </c>
+      <c r="B135" t="s">
+        <v>236</v>
+      </c>
+      <c r="C135" t="s">
         <v>283</v>
       </c>
-      <c r="B135" t="s">
-        <v>279</v>
-      </c>
-      <c r="C135" t="s">
-        <v>284</v>
-      </c>
       <c r="D135" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -6009,16 +6192,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>284</v>
+      </c>
+      <c r="B136" t="s">
+        <v>236</v>
+      </c>
+      <c r="C136" t="s">
         <v>285</v>
       </c>
-      <c r="B136" t="s">
-        <v>279</v>
-      </c>
-      <c r="C136" t="s">
-        <v>286</v>
-      </c>
       <c r="D136" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
@@ -6029,16 +6212,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>286</v>
+      </c>
+      <c r="B137" t="s">
+        <v>236</v>
+      </c>
+      <c r="C137" t="s">
         <v>287</v>
       </c>
-      <c r="B137" t="s">
-        <v>279</v>
-      </c>
-      <c r="C137" t="s">
-        <v>288</v>
-      </c>
       <c r="D137" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
@@ -6049,16 +6232,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>288</v>
+      </c>
+      <c r="B138" t="s">
+        <v>236</v>
+      </c>
+      <c r="C138" t="s">
         <v>289</v>
       </c>
-      <c r="B138" t="s">
-        <v>279</v>
-      </c>
-      <c r="C138" t="s">
-        <v>290</v>
-      </c>
       <c r="D138" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
@@ -6069,16 +6252,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>290</v>
+      </c>
+      <c r="B139" t="s">
+        <v>236</v>
+      </c>
+      <c r="C139" t="s">
         <v>291</v>
       </c>
-      <c r="B139" t="s">
-        <v>279</v>
-      </c>
-      <c r="C139" t="s">
-        <v>292</v>
-      </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -6089,16 +6272,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>292</v>
+      </c>
+      <c r="B140" t="s">
+        <v>236</v>
+      </c>
+      <c r="C140" t="s">
         <v>293</v>
       </c>
-      <c r="B140" t="s">
-        <v>279</v>
-      </c>
-      <c r="C140" t="s">
-        <v>294</v>
-      </c>
       <c r="D140" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
@@ -6109,16 +6292,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>294</v>
+      </c>
+      <c r="B141" t="s">
+        <v>236</v>
+      </c>
+      <c r="C141" t="s">
         <v>295</v>
       </c>
-      <c r="B141" t="s">
-        <v>279</v>
-      </c>
-      <c r="C141" t="s">
-        <v>296</v>
-      </c>
       <c r="D141" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
@@ -6129,16 +6312,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>296</v>
+      </c>
+      <c r="B142" t="s">
         <v>297</v>
-      </c>
-      <c r="B142" t="s">
-        <v>279</v>
       </c>
       <c r="C142" t="s">
         <v>298</v>
       </c>
       <c r="D142" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -6152,13 +6335,13 @@
         <v>299</v>
       </c>
       <c r="B143" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C143" t="s">
         <v>300</v>
       </c>
       <c r="D143" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -6172,13 +6355,13 @@
         <v>301</v>
       </c>
       <c r="B144" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C144" t="s">
         <v>302</v>
       </c>
       <c r="D144" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
@@ -6192,13 +6375,13 @@
         <v>303</v>
       </c>
       <c r="B145" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C145" t="s">
         <v>304</v>
       </c>
       <c r="D145" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
@@ -6212,13 +6395,13 @@
         <v>305</v>
       </c>
       <c r="B146" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C146" t="s">
         <v>306</v>
       </c>
       <c r="D146" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -6232,13 +6415,13 @@
         <v>307</v>
       </c>
       <c r="B147" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C147" t="s">
         <v>308</v>
       </c>
       <c r="D147" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
@@ -6252,13 +6435,13 @@
         <v>309</v>
       </c>
       <c r="B148" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C148" t="s">
         <v>310</v>
       </c>
       <c r="D148" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
@@ -6272,13 +6455,13 @@
         <v>311</v>
       </c>
       <c r="B149" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C149" t="s">
         <v>312</v>
       </c>
       <c r="D149" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
@@ -6292,13 +6475,13 @@
         <v>313</v>
       </c>
       <c r="B150" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C150" t="s">
         <v>314</v>
       </c>
       <c r="D150" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
@@ -6312,13 +6495,13 @@
         <v>315</v>
       </c>
       <c r="B151" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C151" t="s">
         <v>316</v>
       </c>
       <c r="D151" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
@@ -6332,13 +6515,13 @@
         <v>317</v>
       </c>
       <c r="B152" t="s">
+        <v>297</v>
+      </c>
+      <c r="C152" t="s">
         <v>318</v>
       </c>
-      <c r="C152" t="s">
-        <v>319</v>
-      </c>
       <c r="D152" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
@@ -6349,16 +6532,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>319</v>
+      </c>
+      <c r="B153" t="s">
+        <v>297</v>
+      </c>
+      <c r="C153" t="s">
         <v>320</v>
       </c>
-      <c r="B153" t="s">
-        <v>318</v>
-      </c>
-      <c r="C153" t="s">
-        <v>321</v>
-      </c>
       <c r="D153" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
@@ -6369,16 +6552,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>321</v>
+      </c>
+      <c r="B154" t="s">
+        <v>297</v>
+      </c>
+      <c r="C154" t="s">
         <v>322</v>
       </c>
-      <c r="B154" t="s">
-        <v>318</v>
-      </c>
-      <c r="C154" t="s">
-        <v>323</v>
-      </c>
       <c r="D154" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
@@ -6389,16 +6572,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>323</v>
+      </c>
+      <c r="B155" t="s">
+        <v>297</v>
+      </c>
+      <c r="C155" t="s">
         <v>324</v>
       </c>
-      <c r="B155" t="s">
-        <v>318</v>
-      </c>
-      <c r="C155" t="s">
-        <v>325</v>
-      </c>
       <c r="D155" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
@@ -6409,16 +6592,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>325</v>
+      </c>
+      <c r="B156" t="s">
+        <v>297</v>
+      </c>
+      <c r="C156" t="s">
         <v>326</v>
       </c>
-      <c r="B156" t="s">
-        <v>318</v>
-      </c>
-      <c r="C156" t="s">
-        <v>327</v>
-      </c>
       <c r="D156" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
@@ -6429,16 +6612,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>327</v>
+      </c>
+      <c r="B157" t="s">
+        <v>297</v>
+      </c>
+      <c r="C157" t="s">
         <v>328</v>
       </c>
-      <c r="B157" t="s">
-        <v>318</v>
-      </c>
-      <c r="C157" t="s">
-        <v>329</v>
-      </c>
       <c r="D157" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
@@ -6449,16 +6632,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>329</v>
+      </c>
+      <c r="B158" t="s">
+        <v>297</v>
+      </c>
+      <c r="C158" t="s">
         <v>330</v>
       </c>
-      <c r="B158" t="s">
-        <v>318</v>
-      </c>
-      <c r="C158" t="s">
-        <v>331</v>
-      </c>
       <c r="D158" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
@@ -6469,16 +6652,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>331</v>
+      </c>
+      <c r="B159" t="s">
+        <v>297</v>
+      </c>
+      <c r="C159" t="s">
         <v>332</v>
       </c>
-      <c r="B159" t="s">
-        <v>318</v>
-      </c>
-      <c r="C159" t="s">
-        <v>333</v>
-      </c>
       <c r="D159" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
@@ -6489,16 +6672,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>333</v>
+      </c>
+      <c r="B160" t="s">
+        <v>297</v>
+      </c>
+      <c r="C160" t="s">
         <v>334</v>
       </c>
-      <c r="B160" t="s">
-        <v>318</v>
-      </c>
-      <c r="C160" t="s">
-        <v>335</v>
-      </c>
       <c r="D160" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
@@ -6509,16 +6692,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>335</v>
+      </c>
+      <c r="B161" t="s">
+        <v>297</v>
+      </c>
+      <c r="C161" t="s">
         <v>336</v>
       </c>
-      <c r="B161" t="s">
-        <v>318</v>
-      </c>
-      <c r="C161" t="s">
-        <v>337</v>
-      </c>
       <c r="D161" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
@@ -6529,16 +6712,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>337</v>
+      </c>
+      <c r="B162" t="s">
         <v>338</v>
-      </c>
-      <c r="B162" t="s">
-        <v>318</v>
       </c>
       <c r="C162" t="s">
         <v>339</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E162" t="s">
         <v>10</v>
@@ -6552,13 +6735,13 @@
         <v>340</v>
       </c>
       <c r="B163" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C163" t="s">
         <v>341</v>
       </c>
       <c r="D163" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
@@ -6572,13 +6755,13 @@
         <v>342</v>
       </c>
       <c r="B164" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C164" t="s">
         <v>343</v>
       </c>
       <c r="D164" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
@@ -6592,13 +6775,13 @@
         <v>344</v>
       </c>
       <c r="B165" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C165" t="s">
         <v>345</v>
       </c>
       <c r="D165" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
@@ -6612,13 +6795,13 @@
         <v>346</v>
       </c>
       <c r="B166" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C166" t="s">
         <v>347</v>
       </c>
       <c r="D166" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
@@ -6632,13 +6815,13 @@
         <v>348</v>
       </c>
       <c r="B167" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C167" t="s">
         <v>349</v>
       </c>
       <c r="D167" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
@@ -6652,13 +6835,13 @@
         <v>350</v>
       </c>
       <c r="B168" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C168" t="s">
         <v>351</v>
       </c>
       <c r="D168" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
@@ -6672,13 +6855,13 @@
         <v>352</v>
       </c>
       <c r="B169" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C169" t="s">
         <v>353</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
@@ -6692,13 +6875,13 @@
         <v>354</v>
       </c>
       <c r="B170" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C170" t="s">
         <v>355</v>
       </c>
       <c r="D170" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E170" t="s">
         <v>10</v>
@@ -6712,13 +6895,13 @@
         <v>356</v>
       </c>
       <c r="B171" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C171" t="s">
         <v>357</v>
       </c>
       <c r="D171" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E171" t="s">
         <v>10</v>
@@ -6732,13 +6915,13 @@
         <v>358</v>
       </c>
       <c r="B172" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C172" t="s">
         <v>359</v>
       </c>
       <c r="D172" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E172" t="s">
         <v>10</v>
@@ -6752,13 +6935,13 @@
         <v>360</v>
       </c>
       <c r="B173" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C173" t="s">
         <v>361</v>
       </c>
       <c r="D173" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E173" t="s">
         <v>10</v>
@@ -6772,13 +6955,13 @@
         <v>362</v>
       </c>
       <c r="B174" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C174" t="s">
         <v>363</v>
       </c>
       <c r="D174" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E174" t="s">
         <v>10</v>
@@ -6792,13 +6975,13 @@
         <v>364</v>
       </c>
       <c r="B175" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C175" t="s">
         <v>365</v>
       </c>
       <c r="D175" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E175" t="s">
         <v>10</v>
@@ -6812,13 +6995,13 @@
         <v>366</v>
       </c>
       <c r="B176" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C176" t="s">
         <v>367</v>
       </c>
       <c r="D176" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E176" t="s">
         <v>10</v>
@@ -6832,13 +7015,13 @@
         <v>368</v>
       </c>
       <c r="B177" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C177" t="s">
         <v>369</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E177" t="s">
         <v>10</v>
@@ -6852,13 +7035,13 @@
         <v>370</v>
       </c>
       <c r="B178" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C178" t="s">
         <v>371</v>
       </c>
       <c r="D178" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E178" t="s">
         <v>10</v>
@@ -6872,13 +7055,13 @@
         <v>372</v>
       </c>
       <c r="B179" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C179" t="s">
         <v>373</v>
       </c>
       <c r="D179" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E179" t="s">
         <v>10</v>
@@ -6892,7 +7075,7 @@
         <v>374</v>
       </c>
       <c r="B180" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C180" t="s">
         <v>375</v>
@@ -6912,7 +7095,7 @@
         <v>376</v>
       </c>
       <c r="B181" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C181" t="s">
         <v>377</v>
@@ -6932,7 +7115,7 @@
         <v>378</v>
       </c>
       <c r="B182" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C182" t="s">
         <v>379</v>
@@ -6952,7 +7135,7 @@
         <v>380</v>
       </c>
       <c r="B183" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C183" t="s">
         <v>381</v>
@@ -6972,13 +7155,13 @@
         <v>382</v>
       </c>
       <c r="B184" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C184" t="s">
         <v>383</v>
       </c>
       <c r="D184" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E184" t="s">
         <v>10</v>
@@ -6992,13 +7175,13 @@
         <v>384</v>
       </c>
       <c r="B185" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C185" t="s">
         <v>385</v>
       </c>
       <c r="D185" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E185" t="s">
         <v>10</v>
@@ -7012,13 +7195,13 @@
         <v>386</v>
       </c>
       <c r="B186" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C186" t="s">
         <v>387</v>
       </c>
       <c r="D186" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E186" t="s">
         <v>10</v>
@@ -7032,13 +7215,13 @@
         <v>388</v>
       </c>
       <c r="B187" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C187" t="s">
         <v>389</v>
       </c>
       <c r="D187" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E187" t="s">
         <v>10</v>
@@ -7052,13 +7235,13 @@
         <v>390</v>
       </c>
       <c r="B188" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C188" t="s">
         <v>391</v>
       </c>
       <c r="D188" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E188" t="s">
         <v>10</v>
@@ -7072,13 +7255,13 @@
         <v>392</v>
       </c>
       <c r="B189" t="s">
+        <v>338</v>
+      </c>
+      <c r="C189" t="s">
         <v>393</v>
       </c>
-      <c r="C189" t="s">
-        <v>394</v>
-      </c>
       <c r="D189" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E189" t="s">
         <v>10</v>
@@ -7089,16 +7272,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>394</v>
+      </c>
+      <c r="B190" t="s">
+        <v>338</v>
+      </c>
+      <c r="C190" t="s">
         <v>395</v>
       </c>
-      <c r="B190" t="s">
-        <v>393</v>
-      </c>
-      <c r="C190" t="s">
-        <v>396</v>
-      </c>
       <c r="D190" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E190" t="s">
         <v>10</v>
@@ -7109,16 +7292,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>396</v>
+      </c>
+      <c r="B191" t="s">
+        <v>338</v>
+      </c>
+      <c r="C191" t="s">
         <v>397</v>
       </c>
-      <c r="B191" t="s">
-        <v>393</v>
-      </c>
-      <c r="C191" t="s">
-        <v>398</v>
-      </c>
       <c r="D191" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E191" t="s">
         <v>10</v>
@@ -7129,16 +7312,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>398</v>
+      </c>
+      <c r="B192" t="s">
+        <v>338</v>
+      </c>
+      <c r="C192" t="s">
         <v>399</v>
       </c>
-      <c r="B192" t="s">
-        <v>393</v>
-      </c>
-      <c r="C192" t="s">
-        <v>400</v>
-      </c>
       <c r="D192" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E192" t="s">
         <v>10</v>
@@ -7149,16 +7332,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>400</v>
+      </c>
+      <c r="B193" t="s">
+        <v>338</v>
+      </c>
+      <c r="C193" t="s">
         <v>401</v>
       </c>
-      <c r="B193" t="s">
-        <v>393</v>
-      </c>
-      <c r="C193" t="s">
-        <v>402</v>
-      </c>
       <c r="D193" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E193" t="s">
         <v>10</v>
@@ -7169,16 +7352,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>402</v>
+      </c>
+      <c r="B194" t="s">
+        <v>338</v>
+      </c>
+      <c r="C194" t="s">
         <v>403</v>
       </c>
-      <c r="B194" t="s">
-        <v>393</v>
-      </c>
-      <c r="C194" t="s">
-        <v>404</v>
-      </c>
       <c r="D194" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E194" t="s">
         <v>10</v>
@@ -7189,16 +7372,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>404</v>
+      </c>
+      <c r="B195" t="s">
+        <v>338</v>
+      </c>
+      <c r="C195" t="s">
         <v>405</v>
       </c>
-      <c r="B195" t="s">
-        <v>393</v>
-      </c>
-      <c r="C195" t="s">
-        <v>406</v>
-      </c>
       <c r="D195" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E195" t="s">
         <v>10</v>
@@ -7209,16 +7392,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>406</v>
+      </c>
+      <c r="B196" t="s">
+        <v>338</v>
+      </c>
+      <c r="C196" t="s">
         <v>407</v>
       </c>
-      <c r="B196" t="s">
-        <v>393</v>
-      </c>
-      <c r="C196" t="s">
-        <v>408</v>
-      </c>
       <c r="D196" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E196" t="s">
         <v>10</v>
@@ -7229,16 +7412,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>408</v>
+      </c>
+      <c r="B197" t="s">
+        <v>338</v>
+      </c>
+      <c r="C197" t="s">
         <v>409</v>
       </c>
-      <c r="B197" t="s">
-        <v>393</v>
-      </c>
-      <c r="C197" t="s">
-        <v>410</v>
-      </c>
       <c r="D197" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E197" t="s">
         <v>10</v>
@@ -7249,16 +7432,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>410</v>
+      </c>
+      <c r="B198" t="s">
+        <v>338</v>
+      </c>
+      <c r="C198" t="s">
         <v>411</v>
       </c>
-      <c r="B198" t="s">
-        <v>393</v>
-      </c>
-      <c r="C198" t="s">
-        <v>412</v>
-      </c>
       <c r="D198" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E198" t="s">
         <v>10</v>
@@ -7269,16 +7452,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>412</v>
+      </c>
+      <c r="B199" t="s">
+        <v>338</v>
+      </c>
+      <c r="C199" t="s">
         <v>413</v>
       </c>
-      <c r="B199" t="s">
-        <v>393</v>
-      </c>
-      <c r="C199" t="s">
-        <v>414</v>
-      </c>
       <c r="D199" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E199" t="s">
         <v>10</v>
@@ -7289,16 +7472,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>414</v>
+      </c>
+      <c r="B200" t="s">
+        <v>338</v>
+      </c>
+      <c r="C200" t="s">
         <v>415</v>
       </c>
-      <c r="B200" t="s">
-        <v>393</v>
-      </c>
-      <c r="C200" t="s">
-        <v>416</v>
-      </c>
       <c r="D200" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E200" t="s">
         <v>10</v>
@@ -7309,16 +7492,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>416</v>
+      </c>
+      <c r="B201" t="s">
+        <v>338</v>
+      </c>
+      <c r="C201" t="s">
         <v>417</v>
       </c>
-      <c r="B201" t="s">
-        <v>393</v>
-      </c>
-      <c r="C201" t="s">
-        <v>418</v>
-      </c>
       <c r="D201" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E201" t="s">
         <v>10</v>
@@ -7329,16 +7512,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>418</v>
+      </c>
+      <c r="B202" t="s">
         <v>419</v>
-      </c>
-      <c r="B202" t="s">
-        <v>393</v>
       </c>
       <c r="C202" t="s">
         <v>420</v>
       </c>
       <c r="D202" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E202" t="s">
         <v>10</v>
@@ -7352,13 +7535,13 @@
         <v>421</v>
       </c>
       <c r="B203" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C203" t="s">
         <v>422</v>
       </c>
       <c r="D203" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E203" t="s">
         <v>10</v>
@@ -7372,13 +7555,13 @@
         <v>423</v>
       </c>
       <c r="B204" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C204" t="s">
         <v>424</v>
       </c>
       <c r="D204" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E204" t="s">
         <v>10</v>
@@ -7392,13 +7575,13 @@
         <v>425</v>
       </c>
       <c r="B205" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C205" t="s">
         <v>426</v>
       </c>
       <c r="D205" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E205" t="s">
         <v>10</v>
@@ -7412,13 +7595,13 @@
         <v>427</v>
       </c>
       <c r="B206" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C206" t="s">
         <v>428</v>
       </c>
       <c r="D206" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E206" t="s">
         <v>10</v>
@@ -7432,13 +7615,13 @@
         <v>429</v>
       </c>
       <c r="B207" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C207" t="s">
         <v>430</v>
       </c>
       <c r="D207" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E207" t="s">
         <v>10</v>
@@ -7452,13 +7635,13 @@
         <v>431</v>
       </c>
       <c r="B208" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C208" t="s">
         <v>432</v>
       </c>
       <c r="D208" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E208" t="s">
         <v>10</v>
@@ -7472,13 +7655,13 @@
         <v>433</v>
       </c>
       <c r="B209" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C209" t="s">
         <v>434</v>
       </c>
       <c r="D209" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
@@ -7492,13 +7675,13 @@
         <v>435</v>
       </c>
       <c r="B210" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C210" t="s">
         <v>436</v>
       </c>
       <c r="D210" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E210" t="s">
         <v>10</v>
@@ -7512,13 +7695,13 @@
         <v>437</v>
       </c>
       <c r="B211" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C211" t="s">
         <v>438</v>
       </c>
       <c r="D211" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E211" t="s">
         <v>10</v>
@@ -7532,13 +7715,13 @@
         <v>439</v>
       </c>
       <c r="B212" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C212" t="s">
         <v>440</v>
       </c>
       <c r="D212" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E212" t="s">
         <v>10</v>
@@ -7552,13 +7735,13 @@
         <v>441</v>
       </c>
       <c r="B213" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C213" t="s">
         <v>442</v>
       </c>
       <c r="D213" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E213" t="s">
         <v>10</v>
@@ -7572,13 +7755,13 @@
         <v>443</v>
       </c>
       <c r="B214" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C214" t="s">
         <v>444</v>
       </c>
       <c r="D214" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E214" t="s">
         <v>10</v>
@@ -7592,13 +7775,13 @@
         <v>445</v>
       </c>
       <c r="B215" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C215" t="s">
         <v>446</v>
       </c>
       <c r="D215" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E215" t="s">
         <v>10</v>
@@ -7612,13 +7795,13 @@
         <v>447</v>
       </c>
       <c r="B216" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C216" t="s">
         <v>448</v>
       </c>
       <c r="D216" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
@@ -7632,13 +7815,13 @@
         <v>449</v>
       </c>
       <c r="B217" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C217" t="s">
         <v>450</v>
       </c>
       <c r="D217" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E217" t="s">
         <v>10</v>
@@ -7652,13 +7835,13 @@
         <v>451</v>
       </c>
       <c r="B218" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C218" t="s">
         <v>452</v>
       </c>
       <c r="D218" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
@@ -7672,13 +7855,13 @@
         <v>453</v>
       </c>
       <c r="B219" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C219" t="s">
         <v>454</v>
       </c>
       <c r="D219" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E219" t="s">
         <v>10</v>
@@ -7692,13 +7875,13 @@
         <v>455</v>
       </c>
       <c r="B220" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C220" t="s">
         <v>456</v>
       </c>
       <c r="D220" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E220" t="s">
         <v>10</v>
@@ -7712,7 +7895,7 @@
         <v>457</v>
       </c>
       <c r="B221" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C221" t="s">
         <v>458</v>
@@ -7732,7 +7915,7 @@
         <v>459</v>
       </c>
       <c r="B222" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C222" t="s">
         <v>460</v>
@@ -7752,7 +7935,7 @@
         <v>461</v>
       </c>
       <c r="B223" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C223" t="s">
         <v>462</v>
@@ -7772,7 +7955,7 @@
         <v>463</v>
       </c>
       <c r="B224" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C224" t="s">
         <v>464</v>
@@ -7792,7 +7975,7 @@
         <v>465</v>
       </c>
       <c r="B225" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C225" t="s">
         <v>466</v>
@@ -7812,10 +7995,10 @@
         <v>467</v>
       </c>
       <c r="B226" t="s">
+        <v>419</v>
+      </c>
+      <c r="C226" t="s">
         <v>468</v>
-      </c>
-      <c r="C226" t="s">
-        <v>469</v>
       </c>
       <c r="D226" t="s">
         <v>9</v>
@@ -7829,13 +8012,13 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>469</v>
+      </c>
+      <c r="B227" t="s">
+        <v>419</v>
+      </c>
+      <c r="C227" t="s">
         <v>470</v>
-      </c>
-      <c r="B227" t="s">
-        <v>468</v>
-      </c>
-      <c r="C227" t="s">
-        <v>471</v>
       </c>
       <c r="D227" t="s">
         <v>13</v>
@@ -7849,13 +8032,13 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>471</v>
+      </c>
+      <c r="B228" t="s">
+        <v>419</v>
+      </c>
+      <c r="C228" t="s">
         <v>472</v>
-      </c>
-      <c r="B228" t="s">
-        <v>468</v>
-      </c>
-      <c r="C228" t="s">
-        <v>473</v>
       </c>
       <c r="D228" t="s">
         <v>16</v>
@@ -7869,13 +8052,13 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>473</v>
+      </c>
+      <c r="B229" t="s">
+        <v>419</v>
+      </c>
+      <c r="C229" t="s">
         <v>474</v>
-      </c>
-      <c r="B229" t="s">
-        <v>468</v>
-      </c>
-      <c r="C229" t="s">
-        <v>475</v>
       </c>
       <c r="D229" t="s">
         <v>19</v>
@@ -7889,13 +8072,13 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>475</v>
+      </c>
+      <c r="B230" t="s">
+        <v>419</v>
+      </c>
+      <c r="C230" t="s">
         <v>476</v>
-      </c>
-      <c r="B230" t="s">
-        <v>468</v>
-      </c>
-      <c r="C230" t="s">
-        <v>477</v>
       </c>
       <c r="D230" t="s">
         <v>9</v>
@@ -7909,13 +8092,13 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>477</v>
+      </c>
+      <c r="B231" t="s">
+        <v>419</v>
+      </c>
+      <c r="C231" t="s">
         <v>478</v>
-      </c>
-      <c r="B231" t="s">
-        <v>468</v>
-      </c>
-      <c r="C231" t="s">
-        <v>479</v>
       </c>
       <c r="D231" t="s">
         <v>13</v>
@@ -7929,13 +8112,13 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>479</v>
+      </c>
+      <c r="B232" t="s">
+        <v>419</v>
+      </c>
+      <c r="C232" t="s">
         <v>480</v>
-      </c>
-      <c r="B232" t="s">
-        <v>468</v>
-      </c>
-      <c r="C232" t="s">
-        <v>481</v>
       </c>
       <c r="D232" t="s">
         <v>16</v>
@@ -7949,13 +8132,13 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>481</v>
+      </c>
+      <c r="B233" t="s">
+        <v>419</v>
+      </c>
+      <c r="C233" t="s">
         <v>482</v>
-      </c>
-      <c r="B233" t="s">
-        <v>468</v>
-      </c>
-      <c r="C233" t="s">
-        <v>483</v>
       </c>
       <c r="D233" t="s">
         <v>19</v>
@@ -7969,13 +8152,13 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>483</v>
+      </c>
+      <c r="B234" t="s">
+        <v>419</v>
+      </c>
+      <c r="C234" t="s">
         <v>484</v>
-      </c>
-      <c r="B234" t="s">
-        <v>468</v>
-      </c>
-      <c r="C234" t="s">
-        <v>485</v>
       </c>
       <c r="D234" t="s">
         <v>9</v>
@@ -7989,13 +8172,13 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>485</v>
+      </c>
+      <c r="B235" t="s">
+        <v>419</v>
+      </c>
+      <c r="C235" t="s">
         <v>486</v>
-      </c>
-      <c r="B235" t="s">
-        <v>468</v>
-      </c>
-      <c r="C235" t="s">
-        <v>487</v>
       </c>
       <c r="D235" t="s">
         <v>13</v>
@@ -8009,13 +8192,13 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>487</v>
+      </c>
+      <c r="B236" t="s">
+        <v>419</v>
+      </c>
+      <c r="C236" t="s">
         <v>488</v>
-      </c>
-      <c r="B236" t="s">
-        <v>468</v>
-      </c>
-      <c r="C236" t="s">
-        <v>489</v>
       </c>
       <c r="D236" t="s">
         <v>16</v>
@@ -8029,13 +8212,13 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>489</v>
+      </c>
+      <c r="B237" t="s">
+        <v>419</v>
+      </c>
+      <c r="C237" t="s">
         <v>490</v>
-      </c>
-      <c r="B237" t="s">
-        <v>468</v>
-      </c>
-      <c r="C237" t="s">
-        <v>491</v>
       </c>
       <c r="D237" t="s">
         <v>19</v>
@@ -8049,13 +8232,13 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>491</v>
+      </c>
+      <c r="B238" t="s">
+        <v>419</v>
+      </c>
+      <c r="C238" t="s">
         <v>492</v>
-      </c>
-      <c r="B238" t="s">
-        <v>468</v>
-      </c>
-      <c r="C238" t="s">
-        <v>493</v>
       </c>
       <c r="D238" t="s">
         <v>9</v>
@@ -8069,13 +8252,13 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>493</v>
+      </c>
+      <c r="B239" t="s">
+        <v>419</v>
+      </c>
+      <c r="C239" t="s">
         <v>494</v>
-      </c>
-      <c r="B239" t="s">
-        <v>468</v>
-      </c>
-      <c r="C239" t="s">
-        <v>495</v>
       </c>
       <c r="D239" t="s">
         <v>13</v>
@@ -8089,16 +8272,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>495</v>
+      </c>
+      <c r="B240" t="s">
+        <v>419</v>
+      </c>
+      <c r="C240" t="s">
         <v>496</v>
       </c>
-      <c r="B240" t="s">
-        <v>468</v>
-      </c>
-      <c r="C240" t="s">
-        <v>497</v>
-      </c>
       <c r="D240" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E240" t="s">
         <v>10</v>
@@ -8109,16 +8292,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>497</v>
+      </c>
+      <c r="B241" t="s">
+        <v>419</v>
+      </c>
+      <c r="C241" t="s">
         <v>498</v>
       </c>
-      <c r="B241" t="s">
-        <v>468</v>
-      </c>
-      <c r="C241" t="s">
-        <v>499</v>
-      </c>
       <c r="D241" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E241" t="s">
         <v>10</v>
@@ -8129,16 +8312,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>499</v>
+      </c>
+      <c r="B242" t="s">
         <v>500</v>
-      </c>
-      <c r="B242" t="s">
-        <v>468</v>
       </c>
       <c r="C242" t="s">
         <v>501</v>
       </c>
       <c r="D242" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E242" t="s">
         <v>10</v>
@@ -8152,13 +8335,13 @@
         <v>502</v>
       </c>
       <c r="B243" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="C243" t="s">
         <v>503</v>
       </c>
       <c r="D243" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E243" t="s">
         <v>10</v>
@@ -8172,13 +8355,13 @@
         <v>504</v>
       </c>
       <c r="B244" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="C244" t="s">
         <v>505</v>
       </c>
       <c r="D244" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E244" t="s">
         <v>10</v>
@@ -8192,13 +8375,13 @@
         <v>506</v>
       </c>
       <c r="B245" t="s">
+        <v>500</v>
+      </c>
+      <c r="C245" t="s">
         <v>507</v>
       </c>
-      <c r="C245" t="s">
-        <v>508</v>
-      </c>
       <c r="D245" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E245" t="s">
         <v>10</v>
@@ -8209,16 +8392,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>508</v>
+      </c>
+      <c r="B246" t="s">
+        <v>500</v>
+      </c>
+      <c r="C246" t="s">
         <v>509</v>
       </c>
-      <c r="B246" t="s">
-        <v>507</v>
-      </c>
-      <c r="C246" t="s">
-        <v>510</v>
-      </c>
       <c r="D246" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E246" t="s">
         <v>10</v>
@@ -8229,16 +8412,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>510</v>
+      </c>
+      <c r="B247" t="s">
+        <v>500</v>
+      </c>
+      <c r="C247" t="s">
         <v>511</v>
       </c>
-      <c r="B247" t="s">
-        <v>507</v>
-      </c>
-      <c r="C247" t="s">
-        <v>512</v>
-      </c>
       <c r="D247" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E247" t="s">
         <v>10</v>
@@ -8249,16 +8432,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>512</v>
+      </c>
+      <c r="B248" t="s">
+        <v>500</v>
+      </c>
+      <c r="C248" t="s">
         <v>513</v>
       </c>
-      <c r="B248" t="s">
-        <v>507</v>
-      </c>
-      <c r="C248" t="s">
-        <v>514</v>
-      </c>
       <c r="D248" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E248" t="s">
         <v>10</v>
@@ -8269,16 +8452,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>514</v>
+      </c>
+      <c r="B249" t="s">
+        <v>500</v>
+      </c>
+      <c r="C249" t="s">
         <v>515</v>
       </c>
-      <c r="B249" t="s">
-        <v>507</v>
-      </c>
-      <c r="C249" t="s">
-        <v>516</v>
-      </c>
       <c r="D249" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E249" t="s">
         <v>10</v>
@@ -8289,16 +8472,16 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>516</v>
+      </c>
+      <c r="B250" t="s">
+        <v>500</v>
+      </c>
+      <c r="C250" t="s">
         <v>517</v>
       </c>
-      <c r="B250" t="s">
-        <v>507</v>
-      </c>
-      <c r="C250" t="s">
-        <v>518</v>
-      </c>
       <c r="D250" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E250" t="s">
         <v>10</v>
@@ -8309,16 +8492,16 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>518</v>
+      </c>
+      <c r="B251" t="s">
+        <v>500</v>
+      </c>
+      <c r="C251" t="s">
         <v>519</v>
       </c>
-      <c r="B251" t="s">
-        <v>507</v>
-      </c>
-      <c r="C251" t="s">
-        <v>520</v>
-      </c>
       <c r="D251" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E251" t="s">
         <v>10</v>
@@ -8329,16 +8512,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>520</v>
+      </c>
+      <c r="B252" t="s">
+        <v>500</v>
+      </c>
+      <c r="C252" t="s">
         <v>521</v>
       </c>
-      <c r="B252" t="s">
-        <v>507</v>
-      </c>
-      <c r="C252" t="s">
-        <v>522</v>
-      </c>
       <c r="D252" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E252" t="s">
         <v>10</v>
@@ -8349,16 +8532,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>522</v>
+      </c>
+      <c r="B253" t="s">
+        <v>500</v>
+      </c>
+      <c r="C253" t="s">
         <v>523</v>
       </c>
-      <c r="B253" t="s">
-        <v>507</v>
-      </c>
-      <c r="C253" t="s">
-        <v>524</v>
-      </c>
       <c r="D253" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E253" t="s">
         <v>10</v>
@@ -8369,16 +8552,16 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>524</v>
+      </c>
+      <c r="B254" t="s">
+        <v>500</v>
+      </c>
+      <c r="C254" t="s">
         <v>525</v>
       </c>
-      <c r="B254" t="s">
-        <v>507</v>
-      </c>
-      <c r="C254" t="s">
-        <v>526</v>
-      </c>
       <c r="D254" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E254" t="s">
         <v>10</v>
@@ -8389,16 +8572,16 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>526</v>
+      </c>
+      <c r="B255" t="s">
+        <v>500</v>
+      </c>
+      <c r="C255" t="s">
         <v>527</v>
       </c>
-      <c r="B255" t="s">
-        <v>507</v>
-      </c>
-      <c r="C255" t="s">
-        <v>528</v>
-      </c>
       <c r="D255" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E255" t="s">
         <v>10</v>
@@ -8409,16 +8592,16 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>528</v>
+      </c>
+      <c r="B256" t="s">
+        <v>500</v>
+      </c>
+      <c r="C256" t="s">
         <v>529</v>
       </c>
-      <c r="B256" t="s">
-        <v>507</v>
-      </c>
-      <c r="C256" t="s">
-        <v>530</v>
-      </c>
       <c r="D256" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E256" t="s">
         <v>10</v>
@@ -8429,16 +8612,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>530</v>
+      </c>
+      <c r="B257" t="s">
+        <v>500</v>
+      </c>
+      <c r="C257" t="s">
         <v>531</v>
       </c>
-      <c r="B257" t="s">
-        <v>507</v>
-      </c>
-      <c r="C257" t="s">
-        <v>532</v>
-      </c>
       <c r="D257" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E257" t="s">
         <v>10</v>
@@ -8449,16 +8632,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>532</v>
+      </c>
+      <c r="B258" t="s">
+        <v>500</v>
+      </c>
+      <c r="C258" t="s">
         <v>533</v>
       </c>
-      <c r="B258" t="s">
-        <v>507</v>
-      </c>
-      <c r="C258" t="s">
-        <v>534</v>
-      </c>
       <c r="D258" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E258" t="s">
         <v>10</v>
@@ -8469,16 +8652,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>534</v>
+      </c>
+      <c r="B259" t="s">
+        <v>500</v>
+      </c>
+      <c r="C259" t="s">
         <v>535</v>
       </c>
-      <c r="B259" t="s">
-        <v>507</v>
-      </c>
-      <c r="C259" t="s">
-        <v>536</v>
-      </c>
       <c r="D259" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E259" t="s">
         <v>10</v>
@@ -8489,16 +8672,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>536</v>
+      </c>
+      <c r="B260" t="s">
+        <v>500</v>
+      </c>
+      <c r="C260" t="s">
         <v>537</v>
       </c>
-      <c r="B260" t="s">
-        <v>507</v>
-      </c>
-      <c r="C260" t="s">
-        <v>538</v>
-      </c>
       <c r="D260" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E260" t="s">
         <v>10</v>
@@ -8509,16 +8692,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>538</v>
+      </c>
+      <c r="B261" t="s">
+        <v>500</v>
+      </c>
+      <c r="C261" t="s">
         <v>539</v>
       </c>
-      <c r="B261" t="s">
-        <v>507</v>
-      </c>
-      <c r="C261" t="s">
-        <v>540</v>
-      </c>
       <c r="D261" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E261" t="s">
         <v>10</v>
@@ -8529,16 +8712,16 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>540</v>
+      </c>
+      <c r="B262" t="s">
         <v>541</v>
-      </c>
-      <c r="B262" t="s">
-        <v>507</v>
       </c>
       <c r="C262" t="s">
         <v>542</v>
       </c>
       <c r="D262" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E262" t="s">
         <v>10</v>
@@ -8552,13 +8735,13 @@
         <v>543</v>
       </c>
       <c r="B263" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
       <c r="C263" t="s">
         <v>544</v>
       </c>
       <c r="D263" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E263" t="s">
         <v>10</v>
@@ -8572,13 +8755,13 @@
         <v>545</v>
       </c>
       <c r="B264" t="s">
+        <v>541</v>
+      </c>
+      <c r="C264" t="s">
         <v>546</v>
       </c>
-      <c r="C264" t="s">
-        <v>547</v>
-      </c>
       <c r="D264" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E264" t="s">
         <v>10</v>
@@ -8589,16 +8772,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>547</v>
+      </c>
+      <c r="B265" t="s">
+        <v>541</v>
+      </c>
+      <c r="C265" t="s">
         <v>548</v>
       </c>
-      <c r="B265" t="s">
-        <v>546</v>
-      </c>
-      <c r="C265" t="s">
-        <v>549</v>
-      </c>
       <c r="D265" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E265" t="s">
         <v>10</v>
@@ -8609,16 +8792,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>549</v>
+      </c>
+      <c r="B266" t="s">
+        <v>541</v>
+      </c>
+      <c r="C266" t="s">
         <v>550</v>
       </c>
-      <c r="B266" t="s">
-        <v>546</v>
-      </c>
-      <c r="C266" t="s">
-        <v>551</v>
-      </c>
       <c r="D266" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E266" t="s">
         <v>10</v>
@@ -8629,16 +8812,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>551</v>
+      </c>
+      <c r="B267" t="s">
+        <v>541</v>
+      </c>
+      <c r="C267" t="s">
         <v>552</v>
       </c>
-      <c r="B267" t="s">
-        <v>546</v>
-      </c>
-      <c r="C267" t="s">
-        <v>553</v>
-      </c>
       <c r="D267" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E267" t="s">
         <v>10</v>
@@ -8649,16 +8832,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>553</v>
+      </c>
+      <c r="B268" t="s">
+        <v>541</v>
+      </c>
+      <c r="C268" t="s">
         <v>554</v>
       </c>
-      <c r="B268" t="s">
-        <v>546</v>
-      </c>
-      <c r="C268" t="s">
-        <v>555</v>
-      </c>
       <c r="D268" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E268" t="s">
         <v>10</v>
@@ -8669,16 +8852,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>555</v>
+      </c>
+      <c r="B269" t="s">
+        <v>541</v>
+      </c>
+      <c r="C269" t="s">
         <v>556</v>
       </c>
-      <c r="B269" t="s">
-        <v>546</v>
-      </c>
-      <c r="C269" t="s">
-        <v>557</v>
-      </c>
       <c r="D269" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E269" t="s">
         <v>10</v>
@@ -8689,16 +8872,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>557</v>
+      </c>
+      <c r="B270" t="s">
+        <v>541</v>
+      </c>
+      <c r="C270" t="s">
         <v>558</v>
       </c>
-      <c r="B270" t="s">
-        <v>546</v>
-      </c>
-      <c r="C270" t="s">
-        <v>559</v>
-      </c>
       <c r="D270" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E270" t="s">
         <v>10</v>
@@ -8709,16 +8892,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
+        <v>559</v>
+      </c>
+      <c r="B271" t="s">
+        <v>541</v>
+      </c>
+      <c r="C271" t="s">
         <v>560</v>
       </c>
-      <c r="B271" t="s">
-        <v>546</v>
-      </c>
-      <c r="C271" t="s">
-        <v>561</v>
-      </c>
       <c r="D271" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E271" t="s">
         <v>10</v>
@@ -8729,16 +8912,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>561</v>
+      </c>
+      <c r="B272" t="s">
+        <v>541</v>
+      </c>
+      <c r="C272" t="s">
         <v>562</v>
       </c>
-      <c r="B272" t="s">
-        <v>546</v>
-      </c>
-      <c r="C272" t="s">
-        <v>563</v>
-      </c>
       <c r="D272" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E272" t="s">
         <v>10</v>
@@ -8749,16 +8932,16 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>563</v>
+      </c>
+      <c r="B273" t="s">
+        <v>541</v>
+      </c>
+      <c r="C273" t="s">
         <v>564</v>
       </c>
-      <c r="B273" t="s">
-        <v>546</v>
-      </c>
-      <c r="C273" t="s">
-        <v>565</v>
-      </c>
       <c r="D273" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E273" t="s">
         <v>10</v>
@@ -8769,16 +8952,16 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>565</v>
+      </c>
+      <c r="B274" t="s">
+        <v>541</v>
+      </c>
+      <c r="C274" t="s">
         <v>566</v>
       </c>
-      <c r="B274" t="s">
-        <v>546</v>
-      </c>
-      <c r="C274" t="s">
-        <v>567</v>
-      </c>
       <c r="D274" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E274" t="s">
         <v>10</v>
@@ -8789,16 +8972,16 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
+        <v>567</v>
+      </c>
+      <c r="B275" t="s">
+        <v>541</v>
+      </c>
+      <c r="C275" t="s">
         <v>568</v>
       </c>
-      <c r="B275" t="s">
-        <v>546</v>
-      </c>
-      <c r="C275" t="s">
-        <v>569</v>
-      </c>
       <c r="D275" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E275" t="s">
         <v>10</v>
@@ -8809,16 +8992,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
+        <v>569</v>
+      </c>
+      <c r="B276" t="s">
+        <v>541</v>
+      </c>
+      <c r="C276" t="s">
         <v>570</v>
       </c>
-      <c r="B276" t="s">
-        <v>546</v>
-      </c>
-      <c r="C276" t="s">
-        <v>571</v>
-      </c>
       <c r="D276" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E276" t="s">
         <v>10</v>
@@ -8829,16 +9012,16 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>571</v>
+      </c>
+      <c r="B277" t="s">
+        <v>541</v>
+      </c>
+      <c r="C277" t="s">
         <v>572</v>
       </c>
-      <c r="B277" t="s">
-        <v>546</v>
-      </c>
-      <c r="C277" t="s">
-        <v>573</v>
-      </c>
       <c r="D277" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E277" t="s">
         <v>10</v>
@@ -8849,16 +9032,16 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>573</v>
+      </c>
+      <c r="B278" t="s">
+        <v>541</v>
+      </c>
+      <c r="C278" t="s">
         <v>574</v>
       </c>
-      <c r="B278" t="s">
-        <v>546</v>
-      </c>
-      <c r="C278" t="s">
-        <v>575</v>
-      </c>
       <c r="D278" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E278" t="s">
         <v>10</v>
@@ -8869,16 +9052,16 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>575</v>
+      </c>
+      <c r="B279" t="s">
+        <v>541</v>
+      </c>
+      <c r="C279" t="s">
         <v>576</v>
       </c>
-      <c r="B279" t="s">
-        <v>546</v>
-      </c>
-      <c r="C279" t="s">
-        <v>577</v>
-      </c>
       <c r="D279" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E279" t="s">
         <v>10</v>
@@ -8889,16 +9072,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>577</v>
+      </c>
+      <c r="B280" t="s">
+        <v>541</v>
+      </c>
+      <c r="C280" t="s">
         <v>578</v>
       </c>
-      <c r="B280" t="s">
-        <v>546</v>
-      </c>
-      <c r="C280" t="s">
-        <v>579</v>
-      </c>
       <c r="D280" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E280" t="s">
         <v>10</v>
@@ -8909,16 +9092,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>579</v>
+      </c>
+      <c r="B281" t="s">
+        <v>541</v>
+      </c>
+      <c r="C281" t="s">
         <v>580</v>
       </c>
-      <c r="B281" t="s">
-        <v>546</v>
-      </c>
-      <c r="C281" t="s">
-        <v>581</v>
-      </c>
       <c r="D281" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E281" t="s">
         <v>10</v>
@@ -8929,16 +9112,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>581</v>
+      </c>
+      <c r="B282" t="s">
         <v>582</v>
-      </c>
-      <c r="B282" t="s">
-        <v>546</v>
       </c>
       <c r="C282" t="s">
         <v>583</v>
       </c>
       <c r="D282" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E282" t="s">
         <v>10</v>
@@ -8952,13 +9135,13 @@
         <v>584</v>
       </c>
       <c r="B283" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C283" t="s">
         <v>585</v>
       </c>
       <c r="D283" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E283" t="s">
         <v>10</v>
@@ -8972,13 +9155,13 @@
         <v>586</v>
       </c>
       <c r="B284" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C284" t="s">
         <v>587</v>
       </c>
       <c r="D284" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E284" t="s">
         <v>10</v>
@@ -8992,13 +9175,13 @@
         <v>588</v>
       </c>
       <c r="B285" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C285" t="s">
         <v>589</v>
       </c>
       <c r="D285" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E285" t="s">
         <v>10</v>
@@ -9012,13 +9195,13 @@
         <v>590</v>
       </c>
       <c r="B286" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C286" t="s">
         <v>591</v>
       </c>
       <c r="D286" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E286" t="s">
         <v>10</v>
@@ -9032,13 +9215,13 @@
         <v>592</v>
       </c>
       <c r="B287" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C287" t="s">
         <v>593</v>
       </c>
       <c r="D287" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E287" t="s">
         <v>10</v>
@@ -9052,13 +9235,13 @@
         <v>594</v>
       </c>
       <c r="B288" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C288" t="s">
         <v>595</v>
       </c>
       <c r="D288" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E288" t="s">
         <v>10</v>
@@ -9072,13 +9255,13 @@
         <v>596</v>
       </c>
       <c r="B289" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C289" t="s">
         <v>597</v>
       </c>
       <c r="D289" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E289" t="s">
         <v>10</v>
@@ -9092,13 +9275,13 @@
         <v>598</v>
       </c>
       <c r="B290" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C290" t="s">
         <v>599</v>
       </c>
       <c r="D290" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E290" t="s">
         <v>10</v>
@@ -9112,13 +9295,13 @@
         <v>600</v>
       </c>
       <c r="B291" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C291" t="s">
         <v>601</v>
       </c>
       <c r="D291" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E291" t="s">
         <v>10</v>
@@ -9132,7 +9315,7 @@
         <v>602</v>
       </c>
       <c r="B292" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C292" t="s">
         <v>603</v>
@@ -9152,7 +9335,7 @@
         <v>604</v>
       </c>
       <c r="B293" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C293" t="s">
         <v>605</v>
@@ -9172,7 +9355,7 @@
         <v>606</v>
       </c>
       <c r="B294" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C294" t="s">
         <v>607</v>
@@ -9192,7 +9375,7 @@
         <v>608</v>
       </c>
       <c r="B295" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C295" t="s">
         <v>609</v>
@@ -9212,13 +9395,13 @@
         <v>610</v>
       </c>
       <c r="B296" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C296" t="s">
         <v>611</v>
       </c>
       <c r="D296" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E296" t="s">
         <v>10</v>
@@ -9232,13 +9415,13 @@
         <v>612</v>
       </c>
       <c r="B297" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C297" t="s">
         <v>613</v>
       </c>
       <c r="D297" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E297" t="s">
         <v>10</v>
@@ -9252,13 +9435,13 @@
         <v>614</v>
       </c>
       <c r="B298" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C298" t="s">
         <v>615</v>
       </c>
       <c r="D298" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E298" t="s">
         <v>10</v>
@@ -9272,13 +9455,13 @@
         <v>616</v>
       </c>
       <c r="B299" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C299" t="s">
         <v>617</v>
       </c>
       <c r="D299" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E299" t="s">
         <v>10</v>
@@ -9292,13 +9475,13 @@
         <v>618</v>
       </c>
       <c r="B300" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="C300" t="s">
         <v>619</v>
       </c>
       <c r="D300" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E300" t="s">
         <v>10</v>
@@ -9312,13 +9495,13 @@
         <v>620</v>
       </c>
       <c r="B301" t="s">
+        <v>582</v>
+      </c>
+      <c r="C301" t="s">
         <v>621</v>
       </c>
-      <c r="C301" t="s">
-        <v>622</v>
-      </c>
       <c r="D301" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E301" t="s">
         <v>10</v>
@@ -9329,16 +9512,16 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>622</v>
+      </c>
+      <c r="B302" t="s">
+        <v>582</v>
+      </c>
+      <c r="C302" t="s">
         <v>623</v>
       </c>
-      <c r="B302" t="s">
-        <v>621</v>
-      </c>
-      <c r="C302" t="s">
-        <v>624</v>
-      </c>
       <c r="D302" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E302" t="s">
         <v>10</v>
@@ -9349,16 +9532,16 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
+        <v>624</v>
+      </c>
+      <c r="B303" t="s">
+        <v>582</v>
+      </c>
+      <c r="C303" t="s">
         <v>625</v>
       </c>
-      <c r="B303" t="s">
-        <v>621</v>
-      </c>
-      <c r="C303" t="s">
-        <v>626</v>
-      </c>
       <c r="D303" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E303" t="s">
         <v>10</v>
@@ -9369,16 +9552,16 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>626</v>
+      </c>
+      <c r="B304" t="s">
+        <v>582</v>
+      </c>
+      <c r="C304" t="s">
         <v>627</v>
       </c>
-      <c r="B304" t="s">
-        <v>621</v>
-      </c>
-      <c r="C304" t="s">
-        <v>628</v>
-      </c>
       <c r="D304" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E304" t="s">
         <v>10</v>
@@ -9389,16 +9572,16 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
+        <v>628</v>
+      </c>
+      <c r="B305" t="s">
+        <v>582</v>
+      </c>
+      <c r="C305" t="s">
         <v>629</v>
       </c>
-      <c r="B305" t="s">
-        <v>621</v>
-      </c>
-      <c r="C305" t="s">
-        <v>630</v>
-      </c>
       <c r="D305" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E305" t="s">
         <v>10</v>
@@ -9409,16 +9592,16 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>630</v>
+      </c>
+      <c r="B306" t="s">
+        <v>582</v>
+      </c>
+      <c r="C306" t="s">
         <v>631</v>
       </c>
-      <c r="B306" t="s">
-        <v>621</v>
-      </c>
-      <c r="C306" t="s">
-        <v>632</v>
-      </c>
       <c r="D306" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E306" t="s">
         <v>10</v>
@@ -9429,16 +9612,16 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>632</v>
+      </c>
+      <c r="B307" t="s">
+        <v>582</v>
+      </c>
+      <c r="C307" t="s">
         <v>633</v>
       </c>
-      <c r="B307" t="s">
-        <v>621</v>
-      </c>
-      <c r="C307" t="s">
-        <v>634</v>
-      </c>
       <c r="D307" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E307" t="s">
         <v>10</v>
@@ -9449,16 +9632,16 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
+        <v>634</v>
+      </c>
+      <c r="B308" t="s">
+        <v>582</v>
+      </c>
+      <c r="C308" t="s">
         <v>635</v>
       </c>
-      <c r="B308" t="s">
-        <v>621</v>
-      </c>
-      <c r="C308" t="s">
-        <v>636</v>
-      </c>
       <c r="D308" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E308" t="s">
         <v>10</v>
@@ -9469,16 +9652,16 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
+        <v>636</v>
+      </c>
+      <c r="B309" t="s">
+        <v>582</v>
+      </c>
+      <c r="C309" t="s">
         <v>637</v>
       </c>
-      <c r="B309" t="s">
-        <v>621</v>
-      </c>
-      <c r="C309" t="s">
-        <v>638</v>
-      </c>
       <c r="D309" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E309" t="s">
         <v>10</v>
@@ -9489,16 +9672,16 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
+        <v>638</v>
+      </c>
+      <c r="B310" t="s">
+        <v>582</v>
+      </c>
+      <c r="C310" t="s">
         <v>639</v>
       </c>
-      <c r="B310" t="s">
-        <v>621</v>
-      </c>
-      <c r="C310" t="s">
-        <v>640</v>
-      </c>
       <c r="D310" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E310" t="s">
         <v>10</v>
@@ -9509,16 +9692,16 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
+        <v>640</v>
+      </c>
+      <c r="B311" t="s">
+        <v>582</v>
+      </c>
+      <c r="C311" t="s">
         <v>641</v>
       </c>
-      <c r="B311" t="s">
-        <v>621</v>
-      </c>
-      <c r="C311" t="s">
-        <v>642</v>
-      </c>
       <c r="D311" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E311" t="s">
         <v>10</v>
@@ -9529,16 +9712,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
+        <v>642</v>
+      </c>
+      <c r="B312" t="s">
+        <v>582</v>
+      </c>
+      <c r="C312" t="s">
         <v>643</v>
       </c>
-      <c r="B312" t="s">
-        <v>621</v>
-      </c>
-      <c r="C312" t="s">
-        <v>644</v>
-      </c>
       <c r="D312" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E312" t="s">
         <v>10</v>
@@ -9549,16 +9732,16 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
+        <v>644</v>
+      </c>
+      <c r="B313" t="s">
+        <v>582</v>
+      </c>
+      <c r="C313" t="s">
         <v>645</v>
       </c>
-      <c r="B313" t="s">
-        <v>621</v>
-      </c>
-      <c r="C313" t="s">
-        <v>646</v>
-      </c>
       <c r="D313" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E313" t="s">
         <v>10</v>
@@ -9569,16 +9752,16 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
+        <v>646</v>
+      </c>
+      <c r="B314" t="s">
+        <v>582</v>
+      </c>
+      <c r="C314" t="s">
         <v>647</v>
       </c>
-      <c r="B314" t="s">
-        <v>621</v>
-      </c>
-      <c r="C314" t="s">
-        <v>648</v>
-      </c>
       <c r="D314" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E314" t="s">
         <v>10</v>
@@ -9589,16 +9772,16 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
+        <v>648</v>
+      </c>
+      <c r="B315" t="s">
+        <v>582</v>
+      </c>
+      <c r="C315" t="s">
         <v>649</v>
       </c>
-      <c r="B315" t="s">
-        <v>621</v>
-      </c>
-      <c r="C315" t="s">
-        <v>650</v>
-      </c>
       <c r="D315" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E315" t="s">
         <v>10</v>
@@ -9609,16 +9792,16 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
+        <v>650</v>
+      </c>
+      <c r="B316" t="s">
+        <v>582</v>
+      </c>
+      <c r="C316" t="s">
         <v>651</v>
       </c>
-      <c r="B316" t="s">
-        <v>621</v>
-      </c>
-      <c r="C316" t="s">
-        <v>652</v>
-      </c>
       <c r="D316" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E316" t="s">
         <v>10</v>
@@ -9629,16 +9812,16 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
+        <v>652</v>
+      </c>
+      <c r="B317" t="s">
+        <v>582</v>
+      </c>
+      <c r="C317" t="s">
         <v>653</v>
       </c>
-      <c r="B317" t="s">
-        <v>621</v>
-      </c>
-      <c r="C317" t="s">
-        <v>654</v>
-      </c>
       <c r="D317" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E317" t="s">
         <v>10</v>
@@ -9649,16 +9832,16 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
+        <v>654</v>
+      </c>
+      <c r="B318" t="s">
+        <v>582</v>
+      </c>
+      <c r="C318" t="s">
         <v>655</v>
       </c>
-      <c r="B318" t="s">
-        <v>621</v>
-      </c>
-      <c r="C318" t="s">
-        <v>656</v>
-      </c>
       <c r="D318" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E318" t="s">
         <v>10</v>
@@ -9669,16 +9852,16 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>656</v>
+      </c>
+      <c r="B319" t="s">
+        <v>582</v>
+      </c>
+      <c r="C319" t="s">
         <v>657</v>
       </c>
-      <c r="B319" t="s">
-        <v>621</v>
-      </c>
-      <c r="C319" t="s">
-        <v>658</v>
-      </c>
       <c r="D319" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E319" t="s">
         <v>10</v>
@@ -9689,16 +9872,16 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
+        <v>658</v>
+      </c>
+      <c r="B320" t="s">
+        <v>582</v>
+      </c>
+      <c r="C320" t="s">
         <v>659</v>
       </c>
-      <c r="B320" t="s">
-        <v>660</v>
-      </c>
-      <c r="C320" t="s">
-        <v>661</v>
-      </c>
       <c r="D320" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E320" t="s">
         <v>10</v>
@@ -9709,16 +9892,16 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B321" t="s">
-        <v>660</v>
+        <v>582</v>
       </c>
       <c r="C321" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D321" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E321" t="s">
         <v>10</v>
@@ -9729,16 +9912,16 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>662</v>
+      </c>
+      <c r="B322" t="s">
+        <v>663</v>
+      </c>
+      <c r="C322" t="s">
         <v>664</v>
       </c>
-      <c r="B322" t="s">
-        <v>660</v>
-      </c>
-      <c r="C322" t="s">
-        <v>665</v>
-      </c>
       <c r="D322" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E322" t="s">
         <v>10</v>
@@ -9749,16 +9932,16 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
+        <v>665</v>
+      </c>
+      <c r="B323" t="s">
+        <v>663</v>
+      </c>
+      <c r="C323" t="s">
         <v>666</v>
       </c>
-      <c r="B323" t="s">
-        <v>660</v>
-      </c>
-      <c r="C323" t="s">
-        <v>667</v>
-      </c>
       <c r="D323" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E323" t="s">
         <v>10</v>
@@ -9769,16 +9952,16 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
+        <v>667</v>
+      </c>
+      <c r="B324" t="s">
+        <v>663</v>
+      </c>
+      <c r="C324" t="s">
         <v>668</v>
       </c>
-      <c r="B324" t="s">
-        <v>660</v>
-      </c>
-      <c r="C324" t="s">
-        <v>669</v>
-      </c>
       <c r="D324" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E324" t="s">
         <v>10</v>
@@ -9789,16 +9972,16 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
+        <v>669</v>
+      </c>
+      <c r="B325" t="s">
+        <v>663</v>
+      </c>
+      <c r="C325" t="s">
         <v>670</v>
       </c>
-      <c r="B325" t="s">
-        <v>660</v>
-      </c>
-      <c r="C325" t="s">
-        <v>671</v>
-      </c>
       <c r="D325" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E325" t="s">
         <v>10</v>
@@ -9809,16 +9992,16 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
+        <v>671</v>
+      </c>
+      <c r="B326" t="s">
+        <v>663</v>
+      </c>
+      <c r="C326" t="s">
         <v>672</v>
       </c>
-      <c r="B326" t="s">
-        <v>660</v>
-      </c>
-      <c r="C326" t="s">
-        <v>673</v>
-      </c>
       <c r="D326" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E326" t="s">
         <v>10</v>
@@ -9829,16 +10012,16 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
+        <v>673</v>
+      </c>
+      <c r="B327" t="s">
+        <v>663</v>
+      </c>
+      <c r="C327" t="s">
         <v>674</v>
       </c>
-      <c r="B327" t="s">
-        <v>660</v>
-      </c>
-      <c r="C327" t="s">
-        <v>675</v>
-      </c>
       <c r="D327" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E327" t="s">
         <v>10</v>
@@ -9849,16 +10032,16 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>675</v>
+      </c>
+      <c r="B328" t="s">
+        <v>663</v>
+      </c>
+      <c r="C328" t="s">
         <v>676</v>
       </c>
-      <c r="B328" t="s">
-        <v>660</v>
-      </c>
-      <c r="C328" t="s">
-        <v>677</v>
-      </c>
       <c r="D328" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E328" t="s">
         <v>10</v>
@@ -9869,16 +10052,16 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>677</v>
+      </c>
+      <c r="B329" t="s">
+        <v>663</v>
+      </c>
+      <c r="C329" t="s">
         <v>678</v>
       </c>
-      <c r="B329" t="s">
-        <v>660</v>
-      </c>
-      <c r="C329" t="s">
-        <v>679</v>
-      </c>
       <c r="D329" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E329" t="s">
         <v>10</v>
@@ -9889,16 +10072,16 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
+        <v>679</v>
+      </c>
+      <c r="B330" t="s">
+        <v>663</v>
+      </c>
+      <c r="C330" t="s">
         <v>680</v>
       </c>
-      <c r="B330" t="s">
-        <v>660</v>
-      </c>
-      <c r="C330" t="s">
-        <v>681</v>
-      </c>
       <c r="D330" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E330" t="s">
         <v>10</v>
@@ -9909,16 +10092,16 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
+        <v>681</v>
+      </c>
+      <c r="B331" t="s">
+        <v>663</v>
+      </c>
+      <c r="C331" t="s">
         <v>682</v>
       </c>
-      <c r="B331" t="s">
-        <v>660</v>
-      </c>
-      <c r="C331" t="s">
-        <v>683</v>
-      </c>
       <c r="D331" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E331" t="s">
         <v>10</v>
@@ -9929,16 +10112,16 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
+        <v>683</v>
+      </c>
+      <c r="B332" t="s">
+        <v>663</v>
+      </c>
+      <c r="C332" t="s">
         <v>684</v>
       </c>
-      <c r="B332" t="s">
-        <v>660</v>
-      </c>
-      <c r="C332" t="s">
-        <v>685</v>
-      </c>
       <c r="D332" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E332" t="s">
         <v>10</v>
@@ -9949,16 +10132,16 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
+        <v>685</v>
+      </c>
+      <c r="B333" t="s">
+        <v>663</v>
+      </c>
+      <c r="C333" t="s">
         <v>686</v>
       </c>
-      <c r="B333" t="s">
-        <v>660</v>
-      </c>
-      <c r="C333" t="s">
-        <v>687</v>
-      </c>
       <c r="D333" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E333" t="s">
         <v>10</v>
@@ -9969,16 +10152,16 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
+        <v>687</v>
+      </c>
+      <c r="B334" t="s">
+        <v>663</v>
+      </c>
+      <c r="C334" t="s">
         <v>688</v>
       </c>
-      <c r="B334" t="s">
-        <v>660</v>
-      </c>
-      <c r="C334" t="s">
-        <v>689</v>
-      </c>
       <c r="D334" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E334" t="s">
         <v>10</v>
@@ -9989,16 +10172,16 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
+        <v>689</v>
+      </c>
+      <c r="B335" t="s">
+        <v>663</v>
+      </c>
+      <c r="C335" t="s">
         <v>690</v>
       </c>
-      <c r="B335" t="s">
-        <v>660</v>
-      </c>
-      <c r="C335" t="s">
-        <v>691</v>
-      </c>
       <c r="D335" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E335" t="s">
         <v>10</v>
@@ -10009,16 +10192,16 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>691</v>
+      </c>
+      <c r="B336" t="s">
+        <v>663</v>
+      </c>
+      <c r="C336" t="s">
         <v>692</v>
       </c>
-      <c r="B336" t="s">
-        <v>660</v>
-      </c>
-      <c r="C336" t="s">
-        <v>693</v>
-      </c>
       <c r="D336" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E336" t="s">
         <v>10</v>
@@ -10029,16 +10212,16 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>693</v>
+      </c>
+      <c r="B337" t="s">
+        <v>663</v>
+      </c>
+      <c r="C337" t="s">
         <v>694</v>
       </c>
-      <c r="B337" t="s">
-        <v>660</v>
-      </c>
-      <c r="C337" t="s">
-        <v>695</v>
-      </c>
       <c r="D337" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E337" t="s">
         <v>10</v>
@@ -10049,16 +10232,16 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
+        <v>695</v>
+      </c>
+      <c r="B338" t="s">
+        <v>663</v>
+      </c>
+      <c r="C338" t="s">
         <v>696</v>
       </c>
-      <c r="B338" t="s">
-        <v>660</v>
-      </c>
-      <c r="C338" t="s">
-        <v>697</v>
-      </c>
       <c r="D338" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E338" t="s">
         <v>10</v>
@@ -10069,16 +10252,16 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
+        <v>697</v>
+      </c>
+      <c r="B339" t="s">
+        <v>663</v>
+      </c>
+      <c r="C339" t="s">
         <v>698</v>
       </c>
-      <c r="B339" t="s">
-        <v>699</v>
-      </c>
-      <c r="C339" t="s">
-        <v>700</v>
-      </c>
       <c r="D339" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E339" t="s">
         <v>10</v>
@@ -10089,16 +10272,16 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B340" t="s">
-        <v>699</v>
+        <v>663</v>
       </c>
       <c r="C340" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D340" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E340" t="s">
         <v>10</v>
@@ -10109,16 +10292,16 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B341" t="s">
-        <v>699</v>
+        <v>663</v>
       </c>
       <c r="C341" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D341" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E341" t="s">
         <v>10</v>
@@ -10129,16 +10312,16 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
+        <v>703</v>
+      </c>
+      <c r="B342" t="s">
+        <v>704</v>
+      </c>
+      <c r="C342" t="s">
         <v>705</v>
       </c>
-      <c r="B342" t="s">
-        <v>699</v>
-      </c>
-      <c r="C342" t="s">
-        <v>706</v>
-      </c>
       <c r="D342" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E342" t="s">
         <v>10</v>
@@ -10149,16 +10332,16 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
+        <v>706</v>
+      </c>
+      <c r="B343" t="s">
+        <v>704</v>
+      </c>
+      <c r="C343" t="s">
         <v>707</v>
       </c>
-      <c r="B343" t="s">
-        <v>699</v>
-      </c>
-      <c r="C343" t="s">
-        <v>708</v>
-      </c>
       <c r="D343" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E343" t="s">
         <v>10</v>
@@ -10169,16 +10352,16 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
+        <v>708</v>
+      </c>
+      <c r="B344" t="s">
+        <v>704</v>
+      </c>
+      <c r="C344" t="s">
         <v>709</v>
       </c>
-      <c r="B344" t="s">
-        <v>699</v>
-      </c>
-      <c r="C344" t="s">
-        <v>710</v>
-      </c>
       <c r="D344" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E344" t="s">
         <v>10</v>
@@ -10189,16 +10372,16 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
+        <v>710</v>
+      </c>
+      <c r="B345" t="s">
+        <v>704</v>
+      </c>
+      <c r="C345" t="s">
         <v>711</v>
       </c>
-      <c r="B345" t="s">
-        <v>699</v>
-      </c>
-      <c r="C345" t="s">
-        <v>712</v>
-      </c>
       <c r="D345" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E345" t="s">
         <v>10</v>
@@ -10209,16 +10392,16 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
+        <v>712</v>
+      </c>
+      <c r="B346" t="s">
+        <v>704</v>
+      </c>
+      <c r="C346" t="s">
         <v>713</v>
       </c>
-      <c r="B346" t="s">
-        <v>699</v>
-      </c>
-      <c r="C346" t="s">
-        <v>714</v>
-      </c>
       <c r="D346" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E346" t="s">
         <v>10</v>
@@ -10229,16 +10412,16 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
+        <v>714</v>
+      </c>
+      <c r="B347" t="s">
+        <v>704</v>
+      </c>
+      <c r="C347" t="s">
         <v>715</v>
       </c>
-      <c r="B347" t="s">
-        <v>699</v>
-      </c>
-      <c r="C347" t="s">
-        <v>716</v>
-      </c>
       <c r="D347" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E347" t="s">
         <v>10</v>
@@ -10249,16 +10432,16 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
+        <v>716</v>
+      </c>
+      <c r="B348" t="s">
+        <v>704</v>
+      </c>
+      <c r="C348" t="s">
         <v>717</v>
       </c>
-      <c r="B348" t="s">
-        <v>699</v>
-      </c>
-      <c r="C348" t="s">
-        <v>718</v>
-      </c>
       <c r="D348" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E348" t="s">
         <v>10</v>
@@ -10269,16 +10452,16 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>718</v>
+      </c>
+      <c r="B349" t="s">
+        <v>704</v>
+      </c>
+      <c r="C349" t="s">
         <v>719</v>
       </c>
-      <c r="B349" t="s">
-        <v>699</v>
-      </c>
-      <c r="C349" t="s">
-        <v>720</v>
-      </c>
       <c r="D349" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E349" t="s">
         <v>10</v>
@@ -10289,16 +10472,16 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>720</v>
+      </c>
+      <c r="B350" t="s">
+        <v>704</v>
+      </c>
+      <c r="C350" t="s">
         <v>721</v>
       </c>
-      <c r="B350" t="s">
-        <v>699</v>
-      </c>
-      <c r="C350" t="s">
-        <v>722</v>
-      </c>
       <c r="D350" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E350" t="s">
         <v>10</v>
@@ -10309,16 +10492,16 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
+        <v>722</v>
+      </c>
+      <c r="B351" t="s">
+        <v>704</v>
+      </c>
+      <c r="C351" t="s">
         <v>723</v>
       </c>
-      <c r="B351" t="s">
-        <v>699</v>
-      </c>
-      <c r="C351" t="s">
-        <v>724</v>
-      </c>
       <c r="D351" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E351" t="s">
         <v>10</v>
@@ -10329,16 +10512,16 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
+        <v>724</v>
+      </c>
+      <c r="B352" t="s">
+        <v>704</v>
+      </c>
+      <c r="C352" t="s">
         <v>725</v>
       </c>
-      <c r="B352" t="s">
-        <v>699</v>
-      </c>
-      <c r="C352" t="s">
-        <v>726</v>
-      </c>
       <c r="D352" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E352" t="s">
         <v>10</v>
@@ -10349,13 +10532,13 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
+        <v>726</v>
+      </c>
+      <c r="B353" t="s">
+        <v>704</v>
+      </c>
+      <c r="C353" t="s">
         <v>727</v>
-      </c>
-      <c r="B353" t="s">
-        <v>699</v>
-      </c>
-      <c r="C353" t="s">
-        <v>728</v>
       </c>
       <c r="D353" t="s">
         <v>19</v>
@@ -10369,13 +10552,13 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>728</v>
+      </c>
+      <c r="B354" t="s">
+        <v>704</v>
+      </c>
+      <c r="C354" t="s">
         <v>729</v>
-      </c>
-      <c r="B354" t="s">
-        <v>699</v>
-      </c>
-      <c r="C354" t="s">
-        <v>730</v>
       </c>
       <c r="D354" t="s">
         <v>9</v>
@@ -10389,13 +10572,13 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
+        <v>730</v>
+      </c>
+      <c r="B355" t="s">
+        <v>704</v>
+      </c>
+      <c r="C355" t="s">
         <v>731</v>
-      </c>
-      <c r="B355" t="s">
-        <v>699</v>
-      </c>
-      <c r="C355" t="s">
-        <v>732</v>
       </c>
       <c r="D355" t="s">
         <v>13</v>
@@ -10409,13 +10592,13 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
+        <v>732</v>
+      </c>
+      <c r="B356" t="s">
+        <v>704</v>
+      </c>
+      <c r="C356" t="s">
         <v>733</v>
-      </c>
-      <c r="B356" t="s">
-        <v>699</v>
-      </c>
-      <c r="C356" t="s">
-        <v>734</v>
       </c>
       <c r="D356" t="s">
         <v>16</v>
@@ -10429,13 +10612,13 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
+        <v>734</v>
+      </c>
+      <c r="B357" t="s">
+        <v>704</v>
+      </c>
+      <c r="C357" t="s">
         <v>735</v>
-      </c>
-      <c r="B357" t="s">
-        <v>699</v>
-      </c>
-      <c r="C357" t="s">
-        <v>736</v>
       </c>
       <c r="D357" t="s">
         <v>19</v>
@@ -10449,13 +10632,13 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
+        <v>736</v>
+      </c>
+      <c r="B358" t="s">
+        <v>704</v>
+      </c>
+      <c r="C358" t="s">
         <v>737</v>
-      </c>
-      <c r="B358" t="s">
-        <v>738</v>
-      </c>
-      <c r="C358" t="s">
-        <v>739</v>
       </c>
       <c r="D358" t="s">
         <v>9</v>
@@ -10469,13 +10652,13 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B359" t="s">
-        <v>738</v>
+        <v>704</v>
       </c>
       <c r="C359" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D359" t="s">
         <v>13</v>
@@ -10489,13 +10672,13 @@
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B360" t="s">
-        <v>738</v>
+        <v>704</v>
       </c>
       <c r="C360" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D360" t="s">
         <v>16</v>
@@ -10509,13 +10692,13 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B361" t="s">
-        <v>738</v>
+        <v>704</v>
       </c>
       <c r="C361" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D361" t="s">
         <v>19</v>
@@ -10529,13 +10712,13 @@
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>744</v>
+      </c>
+      <c r="B362" t="s">
+        <v>745</v>
+      </c>
+      <c r="C362" t="s">
         <v>746</v>
-      </c>
-      <c r="B362" t="s">
-        <v>738</v>
-      </c>
-      <c r="C362" t="s">
-        <v>747</v>
       </c>
       <c r="D362" t="s">
         <v>9</v>
@@ -10549,13 +10732,13 @@
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
+        <v>747</v>
+      </c>
+      <c r="B363" t="s">
+        <v>745</v>
+      </c>
+      <c r="C363" t="s">
         <v>748</v>
-      </c>
-      <c r="B363" t="s">
-        <v>738</v>
-      </c>
-      <c r="C363" t="s">
-        <v>749</v>
       </c>
       <c r="D363" t="s">
         <v>13</v>
@@ -10569,13 +10752,13 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
+        <v>749</v>
+      </c>
+      <c r="B364" t="s">
+        <v>745</v>
+      </c>
+      <c r="C364" t="s">
         <v>750</v>
-      </c>
-      <c r="B364" t="s">
-        <v>738</v>
-      </c>
-      <c r="C364" t="s">
-        <v>751</v>
       </c>
       <c r="D364" t="s">
         <v>16</v>
@@ -10589,13 +10772,13 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
+        <v>751</v>
+      </c>
+      <c r="B365" t="s">
+        <v>745</v>
+      </c>
+      <c r="C365" t="s">
         <v>752</v>
-      </c>
-      <c r="B365" t="s">
-        <v>738</v>
-      </c>
-      <c r="C365" t="s">
-        <v>753</v>
       </c>
       <c r="D365" t="s">
         <v>19</v>
@@ -10609,13 +10792,13 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>753</v>
+      </c>
+      <c r="B366" t="s">
+        <v>745</v>
+      </c>
+      <c r="C366" t="s">
         <v>754</v>
-      </c>
-      <c r="B366" t="s">
-        <v>738</v>
-      </c>
-      <c r="C366" t="s">
-        <v>755</v>
       </c>
       <c r="D366" t="s">
         <v>9</v>
@@ -10629,13 +10812,13 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
+        <v>755</v>
+      </c>
+      <c r="B367" t="s">
+        <v>745</v>
+      </c>
+      <c r="C367" t="s">
         <v>756</v>
-      </c>
-      <c r="B367" t="s">
-        <v>738</v>
-      </c>
-      <c r="C367" t="s">
-        <v>757</v>
       </c>
       <c r="D367" t="s">
         <v>13</v>
@@ -10649,13 +10832,13 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
+        <v>757</v>
+      </c>
+      <c r="B368" t="s">
+        <v>745</v>
+      </c>
+      <c r="C368" t="s">
         <v>758</v>
-      </c>
-      <c r="B368" t="s">
-        <v>738</v>
-      </c>
-      <c r="C368" t="s">
-        <v>759</v>
       </c>
       <c r="D368" t="s">
         <v>16</v>
@@ -10669,13 +10852,13 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
+        <v>759</v>
+      </c>
+      <c r="B369" t="s">
+        <v>745</v>
+      </c>
+      <c r="C369" t="s">
         <v>760</v>
-      </c>
-      <c r="B369" t="s">
-        <v>738</v>
-      </c>
-      <c r="C369" t="s">
-        <v>761</v>
       </c>
       <c r="D369" t="s">
         <v>19</v>
@@ -10689,13 +10872,13 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
+        <v>761</v>
+      </c>
+      <c r="B370" t="s">
+        <v>745</v>
+      </c>
+      <c r="C370" t="s">
         <v>762</v>
-      </c>
-      <c r="B370" t="s">
-        <v>738</v>
-      </c>
-      <c r="C370" t="s">
-        <v>763</v>
       </c>
       <c r="D370" t="s">
         <v>9</v>
@@ -10709,13 +10892,13 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
+        <v>763</v>
+      </c>
+      <c r="B371" t="s">
+        <v>745</v>
+      </c>
+      <c r="C371" t="s">
         <v>764</v>
-      </c>
-      <c r="B371" t="s">
-        <v>738</v>
-      </c>
-      <c r="C371" t="s">
-        <v>765</v>
       </c>
       <c r="D371" t="s">
         <v>13</v>
@@ -10729,16 +10912,16 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
+        <v>765</v>
+      </c>
+      <c r="B372" t="s">
+        <v>745</v>
+      </c>
+      <c r="C372" t="s">
         <v>766</v>
       </c>
-      <c r="B372" t="s">
-        <v>738</v>
-      </c>
-      <c r="C372" t="s">
-        <v>767</v>
-      </c>
       <c r="D372" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E372" t="s">
         <v>10</v>
@@ -10749,16 +10932,16 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
+        <v>767</v>
+      </c>
+      <c r="B373" t="s">
+        <v>745</v>
+      </c>
+      <c r="C373" t="s">
         <v>768</v>
       </c>
-      <c r="B373" t="s">
-        <v>738</v>
-      </c>
-      <c r="C373" t="s">
-        <v>769</v>
-      </c>
       <c r="D373" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E373" t="s">
         <v>10</v>
@@ -10769,16 +10952,16 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
+        <v>769</v>
+      </c>
+      <c r="B374" t="s">
+        <v>745</v>
+      </c>
+      <c r="C374" t="s">
         <v>770</v>
       </c>
-      <c r="B374" t="s">
-        <v>738</v>
-      </c>
-      <c r="C374" t="s">
-        <v>771</v>
-      </c>
       <c r="D374" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E374" t="s">
         <v>10</v>
@@ -10789,16 +10972,16 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
+        <v>771</v>
+      </c>
+      <c r="B375" t="s">
+        <v>745</v>
+      </c>
+      <c r="C375" t="s">
         <v>772</v>
       </c>
-      <c r="B375" t="s">
-        <v>738</v>
-      </c>
-      <c r="C375" t="s">
-        <v>773</v>
-      </c>
       <c r="D375" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E375" t="s">
         <v>10</v>
@@ -10809,16 +10992,16 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
+        <v>773</v>
+      </c>
+      <c r="B376" t="s">
+        <v>745</v>
+      </c>
+      <c r="C376" t="s">
         <v>774</v>
       </c>
-      <c r="B376" t="s">
-        <v>738</v>
-      </c>
-      <c r="C376" t="s">
-        <v>775</v>
-      </c>
       <c r="D376" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E376" t="s">
         <v>10</v>
@@ -10829,16 +11012,16 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
+        <v>775</v>
+      </c>
+      <c r="B377" t="s">
+        <v>745</v>
+      </c>
+      <c r="C377" t="s">
         <v>776</v>
       </c>
-      <c r="B377" t="s">
-        <v>777</v>
-      </c>
-      <c r="C377" t="s">
-        <v>778</v>
-      </c>
       <c r="D377" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E377" t="s">
         <v>10</v>
@@ -10849,16 +11032,16 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B378" t="s">
-        <v>777</v>
+        <v>745</v>
       </c>
       <c r="C378" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D378" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E378" t="s">
         <v>10</v>
@@ -10869,16 +11052,16 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B379" t="s">
-        <v>777</v>
+        <v>745</v>
       </c>
       <c r="C379" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D379" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E379" t="s">
         <v>10</v>
@@ -10889,16 +11072,16 @@
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B380" t="s">
-        <v>777</v>
+        <v>745</v>
       </c>
       <c r="C380" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D380" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E380" t="s">
         <v>10</v>
@@ -10909,16 +11092,16 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B381" t="s">
-        <v>777</v>
+        <v>745</v>
       </c>
       <c r="C381" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D381" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E381" t="s">
         <v>10</v>
@@ -10929,16 +11112,16 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>785</v>
+      </c>
+      <c r="B382" t="s">
+        <v>786</v>
+      </c>
+      <c r="C382" t="s">
         <v>787</v>
       </c>
-      <c r="B382" t="s">
-        <v>777</v>
-      </c>
-      <c r="C382" t="s">
-        <v>788</v>
-      </c>
       <c r="D382" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E382" t="s">
         <v>10</v>
@@ -10949,16 +11132,16 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
+        <v>788</v>
+      </c>
+      <c r="B383" t="s">
+        <v>786</v>
+      </c>
+      <c r="C383" t="s">
         <v>789</v>
       </c>
-      <c r="B383" t="s">
-        <v>777</v>
-      </c>
-      <c r="C383" t="s">
-        <v>790</v>
-      </c>
       <c r="D383" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E383" t="s">
         <v>10</v>
@@ -10969,16 +11152,16 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
+        <v>790</v>
+      </c>
+      <c r="B384" t="s">
+        <v>786</v>
+      </c>
+      <c r="C384" t="s">
         <v>791</v>
       </c>
-      <c r="B384" t="s">
-        <v>777</v>
-      </c>
-      <c r="C384" t="s">
-        <v>792</v>
-      </c>
       <c r="D384" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E384" t="s">
         <v>10</v>
@@ -10989,16 +11172,16 @@
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
+        <v>792</v>
+      </c>
+      <c r="B385" t="s">
+        <v>786</v>
+      </c>
+      <c r="C385" t="s">
         <v>793</v>
       </c>
-      <c r="B385" t="s">
-        <v>777</v>
-      </c>
-      <c r="C385" t="s">
-        <v>794</v>
-      </c>
       <c r="D385" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E385" t="s">
         <v>10</v>
@@ -11009,16 +11192,16 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
+        <v>794</v>
+      </c>
+      <c r="B386" t="s">
+        <v>786</v>
+      </c>
+      <c r="C386" t="s">
         <v>795</v>
       </c>
-      <c r="B386" t="s">
-        <v>777</v>
-      </c>
-      <c r="C386" t="s">
-        <v>796</v>
-      </c>
       <c r="D386" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E386" t="s">
         <v>10</v>
@@ -11029,16 +11212,16 @@
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
+        <v>796</v>
+      </c>
+      <c r="B387" t="s">
+        <v>786</v>
+      </c>
+      <c r="C387" t="s">
         <v>797</v>
       </c>
-      <c r="B387" t="s">
-        <v>798</v>
-      </c>
-      <c r="C387" t="s">
-        <v>799</v>
-      </c>
       <c r="D387" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E387" t="s">
         <v>10</v>
@@ -11049,16 +11232,16 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B388" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C388" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D388" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E388" t="s">
         <v>10</v>
@@ -11069,16 +11252,16 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B389" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C389" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D389" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E389" t="s">
         <v>10</v>
@@ -11089,16 +11272,16 @@
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B390" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C390" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D390" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E390" t="s">
         <v>10</v>
@@ -11109,16 +11292,16 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B391" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C391" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D391" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E391" t="s">
         <v>10</v>
@@ -11129,16 +11312,16 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B392" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C392" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D392" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E392" t="s">
         <v>10</v>
@@ -11149,16 +11332,16 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B393" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C393" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D393" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E393" t="s">
         <v>10</v>
@@ -11169,16 +11352,16 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B394" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C394" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D394" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E394" t="s">
         <v>10</v>
@@ -11189,16 +11372,16 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B395" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C395" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D395" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E395" t="s">
         <v>10</v>
@@ -11209,16 +11392,16 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B396" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C396" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D396" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E396" t="s">
         <v>10</v>
@@ -11229,16 +11412,16 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B397" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C397" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D397" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E397" t="s">
         <v>10</v>
@@ -11249,16 +11432,16 @@
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B398" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C398" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D398" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E398" t="s">
         <v>10</v>
@@ -11269,16 +11452,16 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B399" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C399" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D399" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E399" t="s">
         <v>10</v>
@@ -11289,16 +11472,16 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B400" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C400" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D400" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E400" t="s">
         <v>10</v>
@@ -11309,13 +11492,13 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B401" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C401" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D401" t="s">
         <v>19</v>
@@ -11329,13 +11512,13 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
+        <v>826</v>
+      </c>
+      <c r="B402" t="s">
+        <v>827</v>
+      </c>
+      <c r="C402" t="s">
         <v>828</v>
-      </c>
-      <c r="B402" t="s">
-        <v>798</v>
-      </c>
-      <c r="C402" t="s">
-        <v>829</v>
       </c>
       <c r="D402" t="s">
         <v>9</v>
@@ -11349,13 +11532,13 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
+        <v>829</v>
+      </c>
+      <c r="B403" t="s">
+        <v>827</v>
+      </c>
+      <c r="C403" t="s">
         <v>830</v>
-      </c>
-      <c r="B403" t="s">
-        <v>798</v>
-      </c>
-      <c r="C403" t="s">
-        <v>831</v>
       </c>
       <c r="D403" t="s">
         <v>13</v>
@@ -11369,13 +11552,13 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
+        <v>831</v>
+      </c>
+      <c r="B404" t="s">
+        <v>827</v>
+      </c>
+      <c r="C404" t="s">
         <v>832</v>
-      </c>
-      <c r="B404" t="s">
-        <v>798</v>
-      </c>
-      <c r="C404" t="s">
-        <v>833</v>
       </c>
       <c r="D404" t="s">
         <v>16</v>
@@ -11389,13 +11572,13 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
+        <v>833</v>
+      </c>
+      <c r="B405" t="s">
+        <v>827</v>
+      </c>
+      <c r="C405" t="s">
         <v>834</v>
-      </c>
-      <c r="B405" t="s">
-        <v>798</v>
-      </c>
-      <c r="C405" t="s">
-        <v>835</v>
       </c>
       <c r="D405" t="s">
         <v>19</v>
@@ -11409,13 +11592,13 @@
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
+        <v>835</v>
+      </c>
+      <c r="B406" t="s">
+        <v>827</v>
+      </c>
+      <c r="C406" t="s">
         <v>836</v>
-      </c>
-      <c r="B406" t="s">
-        <v>837</v>
-      </c>
-      <c r="C406" t="s">
-        <v>838</v>
       </c>
       <c r="D406" t="s">
         <v>9</v>
@@ -11429,13 +11612,13 @@
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B407" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="C407" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D407" t="s">
         <v>13</v>
@@ -11449,13 +11632,13 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B408" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="C408" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D408" t="s">
         <v>16</v>
@@ -11469,13 +11652,13 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B409" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="C409" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D409" t="s">
         <v>19</v>
@@ -11489,13 +11672,13 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B410" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="C410" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D410" t="s">
         <v>9</v>
@@ -11509,13 +11692,13 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B411" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="C411" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D411" t="s">
         <v>13</v>
@@ -11529,16 +11712,16 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
+        <v>847</v>
+      </c>
+      <c r="B412" t="s">
+        <v>848</v>
+      </c>
+      <c r="C412" t="s">
         <v>849</v>
       </c>
-      <c r="B412" t="s">
-        <v>837</v>
-      </c>
-      <c r="C412" t="s">
-        <v>850</v>
-      </c>
       <c r="D412" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E412" t="s">
         <v>10</v>
@@ -11549,16 +11732,16 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
+        <v>850</v>
+      </c>
+      <c r="B413" t="s">
+        <v>848</v>
+      </c>
+      <c r="C413" t="s">
         <v>851</v>
       </c>
-      <c r="B413" t="s">
-        <v>837</v>
-      </c>
-      <c r="C413" t="s">
-        <v>852</v>
-      </c>
       <c r="D413" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E413" t="s">
         <v>10</v>
@@ -11569,16 +11752,16 @@
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
+        <v>852</v>
+      </c>
+      <c r="B414" t="s">
+        <v>848</v>
+      </c>
+      <c r="C414" t="s">
         <v>853</v>
       </c>
-      <c r="B414" t="s">
-        <v>837</v>
-      </c>
-      <c r="C414" t="s">
-        <v>854</v>
-      </c>
       <c r="D414" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E414" t="s">
         <v>10</v>
@@ -11589,16 +11772,16 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
+        <v>854</v>
+      </c>
+      <c r="B415" t="s">
+        <v>848</v>
+      </c>
+      <c r="C415" t="s">
         <v>855</v>
       </c>
-      <c r="B415" t="s">
-        <v>837</v>
-      </c>
-      <c r="C415" t="s">
-        <v>856</v>
-      </c>
       <c r="D415" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E415" t="s">
         <v>10</v>
@@ -11609,13 +11792,13 @@
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
+        <v>856</v>
+      </c>
+      <c r="B416" t="s">
+        <v>848</v>
+      </c>
+      <c r="C416" t="s">
         <v>857</v>
-      </c>
-      <c r="B416" t="s">
-        <v>858</v>
-      </c>
-      <c r="C416" t="s">
-        <v>859</v>
       </c>
       <c r="D416" t="s">
         <v>9</v>
@@ -11629,13 +11812,13 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B417" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C417" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="D417" t="s">
         <v>13</v>
@@ -11649,13 +11832,13 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B418" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C418" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D418" t="s">
         <v>16</v>
@@ -11669,13 +11852,13 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B419" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C419" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D419" t="s">
         <v>19</v>
@@ -11689,13 +11872,13 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B420" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C420" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D420" t="s">
         <v>9</v>
@@ -11709,13 +11892,13 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B421" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C421" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D421" t="s">
         <v>13</v>
@@ -11729,13 +11912,13 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B422" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C422" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D422" t="s">
         <v>16</v>
@@ -11749,13 +11932,13 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B423" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C423" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D423" t="s">
         <v>19</v>
@@ -11769,13 +11952,13 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B424" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C424" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D424" t="s">
         <v>9</v>
@@ -11789,13 +11972,13 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B425" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C425" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D425" t="s">
         <v>13</v>
@@ -11809,13 +11992,13 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B426" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C426" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D426" t="s">
         <v>16</v>
@@ -11829,13 +12012,13 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B427" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C427" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D427" t="s">
         <v>19</v>
@@ -11849,13 +12032,13 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B428" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C428" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D428" t="s">
         <v>9</v>
@@ -11869,13 +12052,13 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B429" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C429" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D429" t="s">
         <v>13</v>
@@ -11889,16 +12072,16 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B430" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C430" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D430" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E430" t="s">
         <v>10</v>
@@ -11909,16 +12092,16 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B431" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C431" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D431" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E431" t="s">
         <v>10</v>
@@ -11929,16 +12112,16 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
+        <v>888</v>
+      </c>
+      <c r="B432" t="s">
+        <v>889</v>
+      </c>
+      <c r="C432" t="s">
         <v>890</v>
       </c>
-      <c r="B432" t="s">
-        <v>858</v>
-      </c>
-      <c r="C432" t="s">
-        <v>891</v>
-      </c>
       <c r="D432" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E432" t="s">
         <v>10</v>
@@ -11949,16 +12132,16 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
+        <v>891</v>
+      </c>
+      <c r="B433" t="s">
+        <v>889</v>
+      </c>
+      <c r="C433" t="s">
         <v>892</v>
       </c>
-      <c r="B433" t="s">
-        <v>858</v>
-      </c>
-      <c r="C433" t="s">
-        <v>893</v>
-      </c>
       <c r="D433" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E433" t="s">
         <v>10</v>
@@ -11969,16 +12152,16 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
+        <v>893</v>
+      </c>
+      <c r="B434" t="s">
+        <v>889</v>
+      </c>
+      <c r="C434" t="s">
         <v>894</v>
       </c>
-      <c r="B434" t="s">
-        <v>858</v>
-      </c>
-      <c r="C434" t="s">
-        <v>895</v>
-      </c>
       <c r="D434" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E434" t="s">
         <v>10</v>
@@ -11989,16 +12172,16 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>143</v>
+        <v>895</v>
       </c>
       <c r="B435" t="s">
+        <v>889</v>
+      </c>
+      <c r="C435" t="s">
         <v>896</v>
       </c>
-      <c r="C435" t="s">
-        <v>897</v>
-      </c>
       <c r="D435" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E435" t="s">
         <v>10</v>
@@ -12009,16 +12192,16 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>146</v>
+        <v>897</v>
       </c>
       <c r="B436" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="C436" t="s">
         <v>898</v>
       </c>
       <c r="D436" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E436" t="s">
         <v>10</v>
@@ -12029,16 +12212,16 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>148</v>
+        <v>899</v>
       </c>
       <c r="B437" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="C437" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D437" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E437" t="s">
         <v>10</v>
@@ -12049,16 +12232,16 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>150</v>
+        <v>901</v>
       </c>
       <c r="B438" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="C438" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D438" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E438" t="s">
         <v>10</v>
@@ -12069,16 +12252,16 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>152</v>
+        <v>903</v>
       </c>
       <c r="B439" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="C439" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D439" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E439" t="s">
         <v>10</v>
@@ -12089,16 +12272,16 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>154</v>
+        <v>905</v>
       </c>
       <c r="B440" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="C440" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="D440" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E440" t="s">
         <v>10</v>
@@ -12109,16 +12292,16 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>156</v>
+        <v>907</v>
       </c>
       <c r="B441" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="C441" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="D441" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E441" t="s">
         <v>10</v>
@@ -12129,16 +12312,16 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>158</v>
+        <v>909</v>
       </c>
       <c r="B442" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C442" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="D442" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E442" t="s">
         <v>10</v>
@@ -12149,16 +12332,16 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>160</v>
+        <v>912</v>
       </c>
       <c r="B443" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C443" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="D443" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E443" t="s">
         <v>10</v>
@@ -12169,16 +12352,16 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>162</v>
+        <v>914</v>
       </c>
       <c r="B444" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C444" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="D444" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E444" t="s">
         <v>10</v>
@@ -12189,16 +12372,16 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>164</v>
+        <v>916</v>
       </c>
       <c r="B445" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C445" t="s">
-        <v>907</v>
+        <v>917</v>
       </c>
       <c r="D445" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E445" t="s">
         <v>10</v>
@@ -12209,16 +12392,16 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>166</v>
+        <v>918</v>
       </c>
       <c r="B446" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C446" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="D446" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E446" t="s">
         <v>10</v>
@@ -12229,16 +12412,16 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>168</v>
+        <v>920</v>
       </c>
       <c r="B447" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C447" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="D447" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E447" t="s">
         <v>10</v>
@@ -12249,16 +12432,16 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>170</v>
+        <v>922</v>
       </c>
       <c r="B448" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C448" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="D448" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E448" t="s">
         <v>10</v>
@@ -12269,13 +12452,13 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>172</v>
+        <v>924</v>
       </c>
       <c r="B449" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C449" t="s">
-        <v>911</v>
+        <v>925</v>
       </c>
       <c r="D449" t="s">
         <v>19</v>
@@ -12289,13 +12472,13 @@
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>174</v>
+        <v>926</v>
       </c>
       <c r="B450" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C450" t="s">
-        <v>912</v>
+        <v>927</v>
       </c>
       <c r="D450" t="s">
         <v>9</v>
@@ -12309,13 +12492,13 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>176</v>
+        <v>928</v>
       </c>
       <c r="B451" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C451" t="s">
-        <v>913</v>
+        <v>929</v>
       </c>
       <c r="D451" t="s">
         <v>13</v>
@@ -12329,13 +12512,13 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>178</v>
+        <v>930</v>
       </c>
       <c r="B452" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C452" t="s">
-        <v>914</v>
+        <v>931</v>
       </c>
       <c r="D452" t="s">
         <v>16</v>
@@ -12349,13 +12532,13 @@
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>180</v>
+        <v>932</v>
       </c>
       <c r="B453" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C453" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
       <c r="D453" t="s">
         <v>19</v>
@@ -12369,13 +12552,13 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="B454" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C454" t="s">
-        <v>917</v>
+        <v>935</v>
       </c>
       <c r="D454" t="s">
         <v>9</v>
@@ -12389,13 +12572,13 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>918</v>
+        <v>936</v>
       </c>
       <c r="B455" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C455" t="s">
-        <v>919</v>
+        <v>937</v>
       </c>
       <c r="D455" t="s">
         <v>13</v>
@@ -12409,13 +12592,13 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>920</v>
+        <v>938</v>
       </c>
       <c r="B456" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C456" t="s">
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="D456" t="s">
         <v>16</v>
@@ -12429,13 +12612,13 @@
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>922</v>
+        <v>940</v>
       </c>
       <c r="B457" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C457" t="s">
-        <v>923</v>
+        <v>941</v>
       </c>
       <c r="D457" t="s">
         <v>19</v>
@@ -12449,13 +12632,13 @@
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>924</v>
+        <v>942</v>
       </c>
       <c r="B458" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C458" t="s">
-        <v>925</v>
+        <v>943</v>
       </c>
       <c r="D458" t="s">
         <v>9</v>
@@ -12469,13 +12652,13 @@
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="B459" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C459" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="D459" t="s">
         <v>13</v>
@@ -12489,13 +12672,13 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>928</v>
+        <v>946</v>
       </c>
       <c r="B460" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C460" t="s">
-        <v>929</v>
+        <v>947</v>
       </c>
       <c r="D460" t="s">
         <v>16</v>
@@ -12509,13 +12692,13 @@
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>930</v>
+        <v>948</v>
       </c>
       <c r="B461" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C461" t="s">
-        <v>931</v>
+        <v>949</v>
       </c>
       <c r="D461" t="s">
         <v>19</v>
@@ -12529,13 +12712,13 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>932</v>
+        <v>153</v>
       </c>
       <c r="B462" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C462" t="s">
-        <v>933</v>
+        <v>951</v>
       </c>
       <c r="D462" t="s">
         <v>9</v>
@@ -12549,16 +12732,16 @@
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>934</v>
+        <v>156</v>
       </c>
       <c r="B463" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C463" t="s">
-        <v>935</v>
+        <v>952</v>
       </c>
       <c r="D463" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E463" t="s">
         <v>10</v>
@@ -12569,16 +12752,16 @@
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>936</v>
+        <v>158</v>
       </c>
       <c r="B464" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C464" t="s">
-        <v>937</v>
+        <v>953</v>
       </c>
       <c r="D464" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E464" t="s">
         <v>10</v>
@@ -12589,16 +12772,16 @@
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>938</v>
+        <v>160</v>
       </c>
       <c r="B465" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C465" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="D465" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E465" t="s">
         <v>10</v>
@@ -12609,16 +12792,16 @@
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>940</v>
+        <v>162</v>
       </c>
       <c r="B466" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C466" t="s">
-        <v>941</v>
+        <v>955</v>
       </c>
       <c r="D466" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E466" t="s">
         <v>10</v>
@@ -12629,16 +12812,16 @@
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>942</v>
+        <v>164</v>
       </c>
       <c r="B467" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C467" t="s">
-        <v>943</v>
+        <v>956</v>
       </c>
       <c r="D467" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E467" t="s">
         <v>10</v>
@@ -12649,16 +12832,16 @@
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>944</v>
+        <v>166</v>
       </c>
       <c r="B468" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C468" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="D468" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E468" t="s">
         <v>10</v>
@@ -12669,16 +12852,16 @@
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>946</v>
+        <v>168</v>
       </c>
       <c r="B469" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C469" t="s">
-        <v>947</v>
+        <v>958</v>
       </c>
       <c r="D469" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E469" t="s">
         <v>10</v>
@@ -12689,16 +12872,16 @@
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>948</v>
+        <v>170</v>
       </c>
       <c r="B470" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C470" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="D470" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E470" t="s">
         <v>10</v>
@@ -12709,16 +12892,16 @@
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
+        <v>172</v>
+      </c>
+      <c r="B471" t="s">
         <v>950</v>
       </c>
-      <c r="B471" t="s">
-        <v>896</v>
-      </c>
       <c r="C471" t="s">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="D471" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E471" t="s">
         <v>10</v>
@@ -12729,16 +12912,16 @@
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>952</v>
+        <v>174</v>
       </c>
       <c r="B472" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C472" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="D472" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E472" t="s">
         <v>10</v>
@@ -12749,16 +12932,16 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>954</v>
+        <v>176</v>
       </c>
       <c r="B473" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C473" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="D473" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E473" t="s">
         <v>10</v>
@@ -12769,16 +12952,16 @@
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>956</v>
+        <v>178</v>
       </c>
       <c r="B474" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C474" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="D474" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E474" t="s">
         <v>10</v>
@@ -12789,16 +12972,16 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>958</v>
+        <v>180</v>
       </c>
       <c r="B475" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C475" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="D475" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E475" t="s">
         <v>10</v>
@@ -12809,16 +12992,16 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>960</v>
+        <v>182</v>
       </c>
       <c r="B476" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C476" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="D476" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E476" t="s">
         <v>10</v>
@@ -12829,16 +13012,16 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>962</v>
+        <v>184</v>
       </c>
       <c r="B477" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C477" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D477" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E477" t="s">
         <v>10</v>
@@ -12849,16 +13032,16 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>964</v>
+        <v>186</v>
       </c>
       <c r="B478" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C478" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D478" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E478" t="s">
         <v>10</v>
@@ -12869,16 +13052,16 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>966</v>
+        <v>188</v>
       </c>
       <c r="B479" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C479" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D479" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E479" t="s">
         <v>10</v>
@@ -12889,21 +13072,641 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>968</v>
+        <v>190</v>
       </c>
       <c r="B480" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="C480" t="s">
         <v>969</v>
       </c>
       <c r="D480" t="s">
+        <v>16</v>
+      </c>
+      <c r="E480" t="s">
+        <v>10</v>
+      </c>
+      <c r="F480">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>192</v>
+      </c>
+      <c r="B481" t="s">
+        <v>950</v>
+      </c>
+      <c r="C481" t="s">
+        <v>970</v>
+      </c>
+      <c r="D481" t="s">
+        <v>19</v>
+      </c>
+      <c r="E481" t="s">
+        <v>10</v>
+      </c>
+      <c r="F481">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>971</v>
+      </c>
+      <c r="B482" t="s">
+        <v>950</v>
+      </c>
+      <c r="C482" t="s">
+        <v>972</v>
+      </c>
+      <c r="D482" t="s">
+        <v>9</v>
+      </c>
+      <c r="E482" t="s">
+        <v>10</v>
+      </c>
+      <c r="F482">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>973</v>
+      </c>
+      <c r="B483" t="s">
+        <v>950</v>
+      </c>
+      <c r="C483" t="s">
+        <v>974</v>
+      </c>
+      <c r="D483" t="s">
         <v>13</v>
       </c>
-      <c r="E480" t="s">
-        <v>10</v>
-      </c>
-      <c r="F480">
+      <c r="E483" t="s">
+        <v>10</v>
+      </c>
+      <c r="F483">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>975</v>
+      </c>
+      <c r="B484" t="s">
+        <v>950</v>
+      </c>
+      <c r="C484" t="s">
+        <v>976</v>
+      </c>
+      <c r="D484" t="s">
+        <v>16</v>
+      </c>
+      <c r="E484" t="s">
+        <v>10</v>
+      </c>
+      <c r="F484">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>977</v>
+      </c>
+      <c r="B485" t="s">
+        <v>950</v>
+      </c>
+      <c r="C485" t="s">
+        <v>978</v>
+      </c>
+      <c r="D485" t="s">
+        <v>19</v>
+      </c>
+      <c r="E485" t="s">
+        <v>10</v>
+      </c>
+      <c r="F485">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>979</v>
+      </c>
+      <c r="B486" t="s">
+        <v>950</v>
+      </c>
+      <c r="C486" t="s">
+        <v>980</v>
+      </c>
+      <c r="D486" t="s">
+        <v>9</v>
+      </c>
+      <c r="E486" t="s">
+        <v>10</v>
+      </c>
+      <c r="F486">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>981</v>
+      </c>
+      <c r="B487" t="s">
+        <v>950</v>
+      </c>
+      <c r="C487" t="s">
+        <v>982</v>
+      </c>
+      <c r="D487" t="s">
+        <v>13</v>
+      </c>
+      <c r="E487" t="s">
+        <v>10</v>
+      </c>
+      <c r="F487">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>983</v>
+      </c>
+      <c r="B488" t="s">
+        <v>950</v>
+      </c>
+      <c r="C488" t="s">
+        <v>984</v>
+      </c>
+      <c r="D488" t="s">
+        <v>16</v>
+      </c>
+      <c r="E488" t="s">
+        <v>10</v>
+      </c>
+      <c r="F488">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>985</v>
+      </c>
+      <c r="B489" t="s">
+        <v>950</v>
+      </c>
+      <c r="C489" t="s">
+        <v>986</v>
+      </c>
+      <c r="D489" t="s">
+        <v>19</v>
+      </c>
+      <c r="E489" t="s">
+        <v>10</v>
+      </c>
+      <c r="F489">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>987</v>
+      </c>
+      <c r="B490" t="s">
+        <v>950</v>
+      </c>
+      <c r="C490" t="s">
+        <v>988</v>
+      </c>
+      <c r="D490" t="s">
+        <v>9</v>
+      </c>
+      <c r="E490" t="s">
+        <v>10</v>
+      </c>
+      <c r="F490">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>989</v>
+      </c>
+      <c r="B491" t="s">
+        <v>950</v>
+      </c>
+      <c r="C491" t="s">
+        <v>990</v>
+      </c>
+      <c r="D491" t="s">
+        <v>13</v>
+      </c>
+      <c r="E491" t="s">
+        <v>10</v>
+      </c>
+      <c r="F491">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>991</v>
+      </c>
+      <c r="B492" t="s">
+        <v>950</v>
+      </c>
+      <c r="C492" t="s">
+        <v>992</v>
+      </c>
+      <c r="D492" t="s">
+        <v>16</v>
+      </c>
+      <c r="E492" t="s">
+        <v>10</v>
+      </c>
+      <c r="F492">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>993</v>
+      </c>
+      <c r="B493" t="s">
+        <v>950</v>
+      </c>
+      <c r="C493" t="s">
+        <v>994</v>
+      </c>
+      <c r="D493" t="s">
+        <v>19</v>
+      </c>
+      <c r="E493" t="s">
+        <v>10</v>
+      </c>
+      <c r="F493">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>995</v>
+      </c>
+      <c r="B494" t="s">
+        <v>950</v>
+      </c>
+      <c r="C494" t="s">
+        <v>996</v>
+      </c>
+      <c r="D494" t="s">
+        <v>9</v>
+      </c>
+      <c r="E494" t="s">
+        <v>10</v>
+      </c>
+      <c r="F494">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>997</v>
+      </c>
+      <c r="B495" t="s">
+        <v>950</v>
+      </c>
+      <c r="C495" t="s">
+        <v>998</v>
+      </c>
+      <c r="D495" t="s">
+        <v>13</v>
+      </c>
+      <c r="E495" t="s">
+        <v>10</v>
+      </c>
+      <c r="F495">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>999</v>
+      </c>
+      <c r="B496" t="s">
+        <v>950</v>
+      </c>
+      <c r="C496" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D496" t="s">
+        <v>16</v>
+      </c>
+      <c r="E496" t="s">
+        <v>10</v>
+      </c>
+      <c r="F496">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B497" t="s">
+        <v>950</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D497" t="s">
+        <v>19</v>
+      </c>
+      <c r="E497" t="s">
+        <v>10</v>
+      </c>
+      <c r="F497">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B498" t="s">
+        <v>950</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D498" t="s">
+        <v>9</v>
+      </c>
+      <c r="E498" t="s">
+        <v>10</v>
+      </c>
+      <c r="F498">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B499" t="s">
+        <v>950</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D499" t="s">
+        <v>13</v>
+      </c>
+      <c r="E499" t="s">
+        <v>10</v>
+      </c>
+      <c r="F499">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B500" t="s">
+        <v>950</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D500" t="s">
+        <v>16</v>
+      </c>
+      <c r="E500" t="s">
+        <v>10</v>
+      </c>
+      <c r="F500">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B501" t="s">
+        <v>950</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D501" t="s">
+        <v>19</v>
+      </c>
+      <c r="E501" t="s">
+        <v>10</v>
+      </c>
+      <c r="F501">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B502" t="s">
+        <v>950</v>
+      </c>
+      <c r="C502" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D502" t="s">
+        <v>9</v>
+      </c>
+      <c r="E502" t="s">
+        <v>10</v>
+      </c>
+      <c r="F502">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B503" t="s">
+        <v>950</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D503" t="s">
+        <v>13</v>
+      </c>
+      <c r="E503" t="s">
+        <v>10</v>
+      </c>
+      <c r="F503">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B504" t="s">
+        <v>950</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D504" t="s">
+        <v>16</v>
+      </c>
+      <c r="E504" t="s">
+        <v>10</v>
+      </c>
+      <c r="F504">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B505" t="s">
+        <v>950</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D505" t="s">
+        <v>19</v>
+      </c>
+      <c r="E505" t="s">
+        <v>10</v>
+      </c>
+      <c r="F505">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B506" t="s">
+        <v>950</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D506" t="s">
+        <v>9</v>
+      </c>
+      <c r="E506" t="s">
+        <v>10</v>
+      </c>
+      <c r="F506">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B507" t="s">
+        <v>950</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D507" t="s">
+        <v>13</v>
+      </c>
+      <c r="E507" t="s">
+        <v>10</v>
+      </c>
+      <c r="F507">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B508" t="s">
+        <v>950</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D508" t="s">
+        <v>16</v>
+      </c>
+      <c r="E508" t="s">
+        <v>10</v>
+      </c>
+      <c r="F508">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B509" t="s">
+        <v>950</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D509" t="s">
+        <v>19</v>
+      </c>
+      <c r="E509" t="s">
+        <v>10</v>
+      </c>
+      <c r="F509">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B510" t="s">
+        <v>950</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D510" t="s">
+        <v>9</v>
+      </c>
+      <c r="E510" t="s">
+        <v>10</v>
+      </c>
+      <c r="F510">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B511" t="s">
+        <v>950</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D511" t="s">
+        <v>13</v>
+      </c>
+      <c r="E511" t="s">
+        <v>10</v>
+      </c>
+      <c r="F511">
         <v>5</v>
       </c>
     </row>
